--- a/outputs/medpar_gap_submission_20261011/MedPAR_Gap_Register_Srikanth.xlsx
+++ b/outputs/medpar_gap_submission_20261011/MedPAR_Gap_Register_Srikanth.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,8 +108,89 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0B6E7F"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF0A2E38"/>
+      <name val="Cambria"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0B6E7F"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF0A2E38"/>
+      <name val="Cambria"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF172033"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -187,8 +268,90 @@
         <fgColor rgb="FF17365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B6E7F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D5CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EBDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F1F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B6E7F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D5CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EBDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F1F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -231,12 +394,56 @@
         <color rgb="FFB3C7CC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB3C7CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB3C7CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB3C7CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB3C7CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB3C7CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB3C7CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB3C7CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB3C7CC"/>
+      </bottom>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -312,6 +519,98 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="4" xfId="2"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="4" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="4" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="4" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="5" xfId="2" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="5" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="5" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="5" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="5" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="5" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="5" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="6" xfId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="6" xfId="3" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="6" xfId="3" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="6" xfId="3" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="7" xfId="3" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="7" xfId="3" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="7" xfId="3" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="7" xfId="3" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="7" xfId="3" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="7" xfId="3" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="7" xfId="3" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -679,7 +978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -687,6 +986,7 @@
     <col width="90" customWidth="1" min="3" max="3"/>
     <col min="4" max="4" width="36" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="95" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="115" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -703,8 +1003,11 @@
       <c r="E1" s="25" t="str">
         <v>Remarks by Srikanth</v>
       </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
+      <c r="F1" s="61" t="str">
+        <v>Reason and closure requirements by Srikanth</v>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Source: Medpar functionality notes V3.pdf (36 pages). Repo: medpar_qa_automation v0.5.0. Checked against the repo's code and config, not its documentation.</t>
@@ -717,6 +1020,9 @@
       </c>
       <c r="E2" s="28" t="str">
         <v>257 tests and five synthetic stages pass. Production acceptance is open. The original baseline at the left is preserved.</v>
+      </c>
+      <c r="F2" s="64" t="str">
+        <v>Partial: a QA check exists, but specified acceptance evidence or part of the approved rule is missing. Blocked: an approved external rule, feed, layout or environment is required before the check can be completed. These are open dependencies, not completed production acceptance. Read the reason/closure column on the matching detailed sheet. The responsible roles below are suggested handoff roles, not confirmed assignments.</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
@@ -725,8 +1031,9 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="28"/>
       <c r="E3" s="28"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
+      <c r="F3" s="64" t="str"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>FIELD COVERAGE (fields named on V3 pages 12-16, plus warning indicators)</t>
@@ -740,6 +1047,7 @@
       <c r="E4" s="28" t="str">
         <v>All 200 fields have registered golden comparison coverage. 195 field entries still require acceptance inputs or independent derivation; five are approved for deletion.</v>
       </c>
+      <c r="F4" s="64" t="str"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -761,6 +1069,7 @@
       <c r="E5" s="28" t="str">
         <v>Original lead finding preserved. See the two new Field Register columns for current implementation and acceptance status.</v>
       </c>
+      <c r="F5" s="64" t="str"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -782,6 +1091,7 @@
       <c r="E6" s="28" t="str">
         <v>Original lead finding preserved. See the two new Field Register columns for current implementation and acceptance status.</v>
       </c>
+      <c r="F6" s="64" t="str"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -803,6 +1113,7 @@
       <c r="E7" s="28" t="str">
         <v>Original lead finding preserved. See the two new Field Register columns for current implementation and acceptance status.</v>
       </c>
+      <c r="F7" s="64" t="str"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -824,6 +1135,7 @@
       <c r="E8" s="28" t="str">
         <v>Original lead finding preserved. See the two new Field Register columns for current implementation and acceptance status.</v>
       </c>
+      <c r="F8" s="64" t="str"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -845,6 +1157,7 @@
       <c r="E9" s="28" t="str">
         <v>Original lead finding preserved. See the two new Field Register columns for current implementation and acceptance status.</v>
       </c>
+      <c r="F9" s="64" t="str"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -862,6 +1175,7 @@
       <c r="E10" s="28" t="str">
         <v>Original lead finding preserved. See the two new Field Register columns for current implementation and acceptance status.</v>
       </c>
+      <c r="F10" s="64" t="str"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="2" t="n"/>
@@ -869,6 +1183,7 @@
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
+      <c r="F11" s="64" t="str"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -884,6 +1199,7 @@
       <c r="E12" s="28" t="str">
         <v>74 rows: 33 done/verified QA checks, 23 partial, 14 blocked on approved inputs, four not required. Done does not mean production certified.</v>
       </c>
+      <c r="F12" s="64" t="str"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -901,6 +1217,7 @@
       <c r="E13" s="28" t="str">
         <v>See Functionality Gaps for row-specific implementation evidence and required inputs.</v>
       </c>
+      <c r="F13" s="64" t="str"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -918,6 +1235,7 @@
       <c r="E14" s="28" t="str">
         <v>See Functionality Gaps for row-specific implementation evidence and required inputs.</v>
       </c>
+      <c r="F14" s="64" t="str"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -935,6 +1253,7 @@
       <c r="E15" s="28" t="str">
         <v>See Functionality Gaps for row-specific implementation evidence and required inputs.</v>
       </c>
+      <c r="F15" s="64" t="str"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -952,6 +1271,7 @@
       <c r="E16" s="28" t="str">
         <v>See Functionality Gaps for row-specific implementation evidence and required inputs.</v>
       </c>
+      <c r="F16" s="64" t="str"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -969,6 +1289,7 @@
       <c r="E17" s="28" t="str">
         <v>See Functionality Gaps for row-specific implementation evidence and required inputs.</v>
       </c>
+      <c r="F17" s="64" t="str"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -986,6 +1307,7 @@
       <c r="E18" s="28" t="str">
         <v>See Functionality Gaps for row-specific implementation evidence and required inputs.</v>
       </c>
+      <c r="F18" s="64" t="str"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -1003,6 +1325,7 @@
       <c r="E19" s="28" t="str">
         <v>See Functionality Gaps for row-specific implementation evidence and required inputs.</v>
       </c>
+      <c r="F19" s="64" t="str"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1024,6 +1347,7 @@
       <c r="E20" s="28" t="str">
         <v>14 rows: six done/verified, six partial, one blocked on performance inputs, one not required.</v>
       </c>
+      <c r="F20" s="64" t="str"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="2" t="n"/>
@@ -1031,6 +1355,7 @@
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="28"/>
       <c r="E21" s="28"/>
+      <c r="F21" s="64" t="str"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1046,6 +1371,7 @@
       <c r="E22" s="28" t="str">
         <v>Original priority/impact counts are unchanged. They are not completion counts.</v>
       </c>
+      <c r="F22" s="64" t="str"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -1067,6 +1393,7 @@
       <c r="E23" s="28" t="str">
         <v>Original priority/impact counts are unchanged. They are not completion counts.</v>
       </c>
+      <c r="F23" s="64" t="str"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1088,6 +1415,7 @@
       <c r="E24" s="28" t="str">
         <v>Original priority/impact counts are unchanged. They are not completion counts.</v>
       </c>
+      <c r="F24" s="64" t="str"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -1109,6 +1437,7 @@
       <c r="E25" s="28" t="str">
         <v>Original priority/impact counts are unchanged. They are not completion counts.</v>
       </c>
+      <c r="F25" s="64" t="str"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1130,6 +1459,7 @@
       <c r="E26" s="28" t="str">
         <v>Original priority/impact counts are unchanged. They are not completion counts.</v>
       </c>
+      <c r="F26" s="64" t="str"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="2" t="n"/>
@@ -1137,8 +1467,9 @@
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="28"/>
       <c r="E27" s="28"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
+      <c r="F27" s="64" t="str"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
           <t>HOW TO READ</t>
@@ -1152,8 +1483,9 @@
       <c r="E28" s="28" t="str">
         <v>Done: documented QA check implemented/verified. Partial: acceptance or part of scope pending. Blocked: approved external input required. Not required: approved deletion/current scope.</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
+      <c r="F28" s="64" t="str"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Gap type: Missing = nothing in the repo; Different = the repo does something else; Conflict = V3 contradicts itself; Config = a setting; Verify = confirm against the COBOL.</t>
@@ -1167,8 +1499,11 @@
       <c r="E29" s="28" t="str">
         <v>Original findings are preserved. New remarks distinguish code/test evidence from missing golden data, layouts, reference mappings and scope decisions.</v>
       </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+      <c r="F29" s="64" t="str">
+        <v>Partial: a QA check exists, but specified acceptance evidence or part of the approved rule is missing. Blocked: an approved external rule, feed, layout or environment is required before the check can be completed. These are open dependencies, not completed production acceptance. Read the reason/closure column on the matching detailed sheet. The responsible roles below are suggested handoff roles, not confirmed assignments.</v>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Business decision needed: Y means an owner must settle the rule before the expected result can be written.</t>
@@ -1182,8 +1517,11 @@
       <c r="E30" s="28" t="str">
         <v>No business policy, missing source value or golden output was invented to produce a Done status.</v>
       </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
+      <c r="F30" s="64" t="str">
+        <v>Partial: a QA check exists, but specified acceptance evidence or part of the approved rule is missing. Blocked: an approved external rule, feed, layout or environment is required before the check can be completed. These are open dependencies, not completed production acceptance. Read the reason/closure column on the matching detailed sheet. The responsible roles below are suggested handoff roles, not confirmed assignments.</v>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Limits: embedded diagrams were read as text only; V3 says some RIF rules are outdated against the COBOL.</t>
@@ -1196,6 +1534,9 @@
       </c>
       <c r="E31" s="28" t="str">
         <v>Current full archive: 1,960 failed and 131 blocked checks. Final MEDPAR has no identifiable production dataset. See README.md and the production report.</v>
+      </c>
+      <c r="F31" s="64" t="str">
+        <v>Partial: a QA check exists, but specified acceptance evidence or part of the approved rule is missing. Blocked: an approved external rule, feed, layout or environment is required before the check can be completed. These are open dependencies, not completed production acceptance. Read the reason/closure column on the matching detailed sheet. The responsible roles below are suggested handoff roles, not confirmed assignments.</v>
       </c>
     </row>
   </sheetData>
@@ -1209,7 +1550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K201"/>
+  <dimension ref="A1:L201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1223,6 +1564,7 @@
     <col width="60" customWidth="1" min="9" max="9"/>
     <col min="10" max="10" width="36" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="95" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="115" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1277,8 +1619,11 @@
       <c r="K1" s="25" t="str">
         <v>Remarks by Srikanth</v>
       </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
+      <c r="L1" s="61" t="str">
+        <v>Reason and closure requirements by Srikanth</v>
+      </c>
+    </row>
+    <row r="2" ht="168" customHeight="1">
       <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
@@ -1326,8 +1671,18 @@
       <c r="K2" s="28" t="str">
         <v>Field MED-DRG-CODE-0531: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
+      <c r="L2" s="64" t="str">
+        <v>Item: 1 — MED-DRG-CODE-0531
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MED-DRG-CODE-0531, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MED-DRG-CODE-0531 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the DRG Lookups group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: DRG lookup by thru date; non-numeric DRG defaults to 999; trailing-space shift. Include the effective DRG/grouper version and licensed lookup/outlier tables used to obtain the expected value.
+Suggested responsible roles: MedPAR grouper/reference-data owner and business acceptance owner.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="3" ht="156" customHeight="1">
       <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
@@ -1375,8 +1730,18 @@
       <c r="K3" s="28" t="str">
         <v>Field MEDPAR-BASE-OPRTG-DRG-AMT-0870: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+      <c r="L3" s="64" t="str">
+        <v>Item: 2 — MEDPAR-BASE-OPRTG-DRG-AMT-0870
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-BASE-OPRTG-DRG-AMT-0870, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-BASE-OPRTG-DRG-AMT-0870 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="4" ht="156" customHeight="1">
       <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
@@ -1424,8 +1789,18 @@
       <c r="K4" s="28" t="str">
         <v>Field MEDPAR-BNDLD-ADJSTMT-AMT-1150: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
+      <c r="L4" s="64" t="str">
+        <v>Item: 3 — MEDPAR-BNDLD-ADJSTMT-AMT-1150
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-BNDLD-ADJSTMT-AMT-1150, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-BNDLD-ADJSTMT-AMT-1150 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="5" ht="156" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
@@ -1473,8 +1848,18 @@
       <c r="K5" s="28" t="str">
         <v>Field MEDPAR-CLM-MODL-REIMB-AMT-1480: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
+      <c r="L5" s="64" t="str">
+        <v>Item: 4 — MEDPAR-CLM-MODL-REIMB-AMT-1480
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-CLM-MODL-REIMB-AMT-1480, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CLM-MODL-REIMB-AMT-1480 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="6" ht="156" customHeight="1">
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
@@ -1522,8 +1907,18 @@
       <c r="K6" s="28" t="str">
         <v>Field MEDPAR-CR-RCV-REPL-DVC-SW-0840: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+      <c r="L6" s="64" t="str">
+        <v>Item: 5 — MEDPAR-CR-RCV-REPL-DVC-SW-0840
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-CR-RCV-REPL-DVC-SW-0840, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CR-RCV-REPL-DVC-SW-0840 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="7" ht="156" customHeight="1">
       <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
@@ -1571,8 +1966,18 @@
       <c r="K7" s="28" t="str">
         <v>Field MEDPAR-DEATH-AFTER-ADM-0611: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+      <c r="L7" s="64" t="str">
+        <v>Item: 6 — MEDPAR-DEATH-AFTER-ADM-0611
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-DEATH-AFTER-ADM-0611, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-DEATH-AFTER-ADM-0611 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Calc. Length of Stay group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: LOS: same day = 1, still patient +1, admit missing -&gt; from date.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="8" ht="156" customHeight="1">
       <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
@@ -1620,8 +2025,18 @@
       <c r="K8" s="28" t="str">
         <v>Field MEDPAR-DGNS-E-CD: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+      <c r="L8" s="64" t="str">
+        <v>Item: 7 — MEDPAR-DGNS-E-CD
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-DGNS-E-CD, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-DGNS-E-CD (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Diag Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: 25 POA/diagnosis (12 E-code) limits, version code, blank POA.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="9" ht="156" customHeight="1">
       <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
@@ -1669,8 +2084,18 @@
       <c r="K9" s="28" t="str">
         <v>Field MEDPAR-DGNS-E-CD-CNT: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+      <c r="L9" s="64" t="str">
+        <v>Item: 8 — MEDPAR-DGNS-E-CD-CNT
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-DGNS-E-CD-CNT, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-DGNS-E-CD-CNT (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Diag Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: 25 POA/diagnosis (12 E-code) limits, version code, blank POA.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="10" ht="156" customHeight="1">
       <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
@@ -1718,8 +2143,18 @@
       <c r="K10" s="28" t="str">
         <v>Field MEDPAR-DGNS-E-VRSN-CD: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+      <c r="L10" s="64" t="str">
+        <v>Item: 9 — MEDPAR-DGNS-E-VRSN-CD
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-DGNS-E-VRSN-CD, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-DGNS-E-VRSN-CD (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Diag Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: 25 POA/diagnosis (12 E-code) limits, version code, blank POA.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="11" ht="156" customHeight="1">
       <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
@@ -1767,8 +2202,18 @@
       <c r="K11" s="28" t="str">
         <v>Field MEDPAR-DGNS-VRSN-CD: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+      <c r="L11" s="64" t="str">
+        <v>Item: 10 — MEDPAR-DGNS-VRSN-CD
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-DGNS-VRSN-CD, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-DGNS-VRSN-CD (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Diag Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: 25 POA/diagnosis (12 E-code) limits, version code, blank POA.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="12" ht="156" customHeight="1">
       <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
@@ -1816,8 +2261,18 @@
       <c r="K12" s="28" t="str">
         <v>Field MEDPAR-DIAG-CODE-0492: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
+      <c r="L12" s="64" t="str">
+        <v>Item: 11 — MEDPAR-DIAG-CODE-0492
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-DIAG-CODE-0492, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-DIAG-CODE-0492 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Diag Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: 25 POA/diagnosis (12 E-code) limits, version code, blank POA.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="13" ht="156" customHeight="1">
       <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
@@ -1865,8 +2320,18 @@
       <c r="K13" s="28" t="str">
         <v>Field MEDPAR-DISPROPORTIONATE-0360: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+      <c r="L13" s="64" t="str">
+        <v>Item: 12 — MEDPAR-DISPROPORTIONATE-0360
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-DISPROPORTIONATE-0360, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-DISPROPORTIONATE-0360 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="14" ht="156" customHeight="1">
       <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
@@ -1914,8 +2379,18 @@
       <c r="K14" s="28" t="str">
         <v>Field MEDPAR-EHR-ADJSTMT-AMT-1180: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
+      <c r="L14" s="64" t="str">
+        <v>Item: 13 — MEDPAR-EHR-ADJSTMT-AMT-1180
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-EHR-ADJSTMT-AMT-1180, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-EHR-ADJSTMT-AMT-1180 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="15" ht="156" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
@@ -1963,8 +2438,18 @@
       <c r="K15" s="28" t="str">
         <v>Field MEDPAR-EMER-USE-SW-1590: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+      <c r="L15" s="64" t="str">
+        <v>Item: 14 — MEDPAR-EMER-USE-SW-1590
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-EMER-USE-SW-1590, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-EMER-USE-SW-1590 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Condition Codes and other group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Code present -&gt; Y, absent -&gt; N, multiple codes, wrong-case code.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="16" ht="156" customHeight="1">
       <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
@@ -2012,8 +2497,18 @@
       <c r="K16" s="28" t="str">
         <v>Field MEDPAR-ESRD-CONDITION-0550: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
+      <c r="L16" s="64" t="str">
+        <v>Item: 15 — MEDPAR-ESRD-CONDITION-0550
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-ESRD-CONDITION-0550, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ESRD-CONDITION-0550 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Condition Codes and other group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Code present -&gt; Y, absent -&gt; N, multiple codes, wrong-case code.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="17" ht="156" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
@@ -2061,8 +2556,18 @@
       <c r="K17" s="28" t="str">
         <v>Field MEDPAR-EXPNDD-ACS-SW-1570: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
+      <c r="L17" s="64" t="str">
+        <v>Item: 16 — MEDPAR-EXPNDD-ACS-SW-1570
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-EXPNDD-ACS-SW-1570, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-EXPNDD-ACS-SW-1570 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Condition Codes and other group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Code present -&gt; Y, absent -&gt; N, multiple codes, wrong-case code.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="18" ht="156" customHeight="1">
       <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
@@ -2110,8 +2615,18 @@
       <c r="K18" s="28" t="str">
         <v>Field MEDPAR-FINL-STD-AMT-1200: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
+      <c r="L18" s="64" t="str">
+        <v>Item: 17 — MEDPAR-FINL-STD-AMT-1200
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-FINL-STD-AMT-1200, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-FINL-STD-AMT-1200 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="19" ht="156" customHeight="1">
       <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
@@ -2159,8 +2674,18 @@
       <c r="K19" s="28" t="str">
         <v>Field MEDPAR-FULL-STD-PMT-AMT-1310: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
+      <c r="L19" s="64" t="str">
+        <v>Item: 18 — MEDPAR-FULL-STD-PMT-AMT-1310
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-FULL-STD-PMT-AMT-1310, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-FULL-STD-PMT-AMT-1310 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="20" ht="156" customHeight="1">
       <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
@@ -2208,8 +2733,18 @@
       <c r="K20" s="28" t="str">
         <v>Field MEDPAR-HAC-RDCTN-PMT-AMT-1210: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+      <c r="L20" s="64" t="str">
+        <v>Item: 19 — MEDPAR-HAC-RDCTN-PMT-AMT-1210
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-HAC-RDCTN-PMT-AMT-1210, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-HAC-RDCTN-PMT-AMT-1210 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="21" ht="156" customHeight="1">
       <c r="A21" s="5" t="n">
         <v>20</v>
       </c>
@@ -2257,8 +2792,18 @@
       <c r="K21" s="28" t="str">
         <v>Field MEDPAR-HIMASTER-DOD-0230: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+      <c r="L21" s="64" t="str">
+        <v>Item: 20 — MEDPAR-HIMASTER-DOD-0230
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-HIMASTER-DOD-0230, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-HIMASTER-DOD-0230 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Get DOD from external file group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: DOD match / no match plus dead status -&gt; thru date and verify switch B.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="22" ht="156" customHeight="1">
       <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
@@ -2306,8 +2851,18 @@
       <c r="K22" s="28" t="str">
         <v>Field MEDPAR-HIMASTER-DOD-IND-0240: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
+      <c r="L22" s="64" t="str">
+        <v>Item: 21 — MEDPAR-HIMASTER-DOD-IND-0240
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-HIMASTER-DOD-IND-0240, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-HIMASTER-DOD-IND-0240 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Get DOD Ind from external file group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: DOD match / no match plus dead status -&gt; thru date and verify switch B.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="23" ht="156" customHeight="1">
       <c r="A23" s="5" t="n">
         <v>22</v>
       </c>
@@ -2355,8 +2910,18 @@
       <c r="K23" s="28" t="str">
         <v>Field MEDPAR-HRR-ADJSTMT-AMT-1170: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
+      <c r="L23" s="64" t="str">
+        <v>Item: 22 — MEDPAR-HRR-ADJSTMT-AMT-1170
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-HRR-ADJSTMT-AMT-1170, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-HRR-ADJSTMT-AMT-1170 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="24" ht="156" customHeight="1">
       <c r="A24" s="5" t="n">
         <v>23</v>
       </c>
@@ -2404,8 +2969,18 @@
       <c r="K24" s="28" t="str">
         <v>Field MEDPAR-IME-AMOUNT-0370: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+      <c r="L24" s="64" t="str">
+        <v>Item: 23 — MEDPAR-IME-AMOUNT-0370
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-IME-AMOUNT-0370, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-IME-AMOUNT-0370 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="25" ht="156" customHeight="1">
       <c r="A25" s="5" t="n">
         <v>24</v>
       </c>
@@ -2453,8 +3028,18 @@
       <c r="K25" s="28" t="str">
         <v>Field MEDPAR-INFOR-ENCTR-IND-SW-0800: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="26" ht="48" customHeight="1">
+      <c r="L25" s="64" t="str">
+        <v>Item: 24 — MEDPAR-INFOR-ENCTR-IND-SW-0800
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-INFOR-ENCTR-IND-SW-0800, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-INFOR-ENCTR-IND-SW-0800 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Condition Codes and other group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Code present -&gt; Y, absent -&gt; N, multiple codes, wrong-case code.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="26" ht="156" customHeight="1">
       <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
@@ -2502,8 +3087,18 @@
       <c r="K26" s="28" t="str">
         <v>Field MEDPAR-ISLET-ADDON-PMTAMT-1450: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
+      <c r="L26" s="64" t="str">
+        <v>Item: 25 — MEDPAR-ISLET-ADDON-PMTAMT-1450
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-ISLET-ADDON-PMTAMT-1450, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ISLET-ADDON-PMTAMT-1450 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="27" ht="156" customHeight="1">
       <c r="A27" s="5" t="n">
         <v>26</v>
       </c>
@@ -2551,8 +3146,18 @@
       <c r="K27" s="28" t="str">
         <v>Field MEDPAR-LGTH-STAY-0260: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
+      <c r="L27" s="64" t="str">
+        <v>Item: 26 — MEDPAR-LGTH-STAY-0260
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-LGTH-STAY-0260, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-LGTH-STAY-0260 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Calc. Length of Stay group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: LOS: same day = 1, still patient +1, admit missing -&gt; from date.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="28" ht="156" customHeight="1">
       <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
@@ -2600,8 +3205,18 @@
       <c r="K28" s="28" t="str">
         <v>Field MEDPAR-LTCH-DPP-ADJ-AMT-1540: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
+      <c r="L28" s="64" t="str">
+        <v>Item: 27 — MEDPAR-LTCH-DPP-ADJ-AMT-1540
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-LTCH-DPP-ADJ-AMT-1540, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-LTCH-DPP-ADJ-AMT-1540 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="29" ht="156" customHeight="1">
       <c r="A29" s="5" t="n">
         <v>28</v>
       </c>
@@ -2649,8 +3264,18 @@
       <c r="K29" s="28" t="str">
         <v>Field MEDPAR-MA-TEACH-IND-SW-0810: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="30" ht="48" customHeight="1">
+      <c r="L29" s="64" t="str">
+        <v>Item: 28 — MEDPAR-MA-TEACH-IND-SW-0810
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-MA-TEACH-IND-SW-0810, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-MA-TEACH-IND-SW-0810 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Condition Codes and other group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Code present -&gt; Y, absent -&gt; N, multiple codes, wrong-case code.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="30" ht="156" customHeight="1">
       <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
@@ -2698,8 +3323,18 @@
       <c r="K30" s="28" t="str">
         <v>Field MEDPAR-NEW-TECH-ADD-O-AMT-0860: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
+      <c r="L30" s="64" t="str">
+        <v>Item: 29 — MEDPAR-NEW-TECH-ADD-O-AMT-0860
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-NEW-TECH-ADD-O-AMT-0860, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-NEW-TECH-ADD-O-AMT-0860 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="31" ht="156" customHeight="1">
       <c r="A31" s="5" t="n">
         <v>30</v>
       </c>
@@ -2747,8 +3382,18 @@
       <c r="K31" s="28" t="str">
         <v>Field MEDPAR-NO-DIAG-CODES-0491: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
+      <c r="L31" s="64" t="str">
+        <v>Item: 30 — MEDPAR-NO-DIAG-CODES-0491
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-NO-DIAG-CODES-0491, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-NO-DIAG-CODES-0491 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Diag Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: 25 POA/diagnosis (12 E-code) limits, version code, blank POA.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="32" ht="156" customHeight="1">
       <c r="A32" s="5" t="n">
         <v>31</v>
       </c>
@@ -2796,8 +3441,18 @@
       <c r="K32" s="28" t="str">
         <v>Field MEDPAR-NO-PSTV-TEST-SW-1560: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
+      <c r="L32" s="64" t="str">
+        <v>Item: 31 — MEDPAR-NO-PSTV-TEST-SW-1560
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-NO-PSTV-TEST-SW-1560, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-NO-PSTV-TEST-SW-1560 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Condition Codes and other group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Code present -&gt; Y, absent -&gt; N, multiple codes, wrong-case code.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="33" ht="156" customHeight="1">
       <c r="A33" s="5" t="n">
         <v>32</v>
       </c>
@@ -2845,8 +3500,18 @@
       <c r="K33" s="28" t="str">
         <v>Field MEDPAR-OPRTG-HSP-AMT-0880: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
+      <c r="L33" s="64" t="str">
+        <v>Item: 32 — MEDPAR-OPRTG-HSP-AMT-0880
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-OPRTG-HSP-AMT-0880, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-OPRTG-HSP-AMT-0880 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="34" ht="156" customHeight="1">
       <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
@@ -2894,8 +3559,18 @@
       <c r="K34" s="28" t="str">
         <v>Field MEDPAR-OTHR-CLNCL-TRIL-SW-1580: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
+      <c r="L34" s="64" t="str">
+        <v>Item: 33 — MEDPAR-OTHR-CLNCL-TRIL-SW-1580
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-OTHR-CLNCL-TRIL-SW-1580, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-OTHR-CLNCL-TRIL-SW-1580 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Condition Codes and other group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Code present -&gt; Y, absent -&gt; N, multiple codes, wrong-case code.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
       <c r="A35" s="5" t="n">
         <v>34</v>
       </c>
@@ -2943,8 +3618,11 @@
       <c r="K35" s="28" t="str">
         <v>Field MEDPAR-OUTLIER-DAYS-0270: Blank/filler deletion check. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. </v>
       </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
+      <c r="L35" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Excluded by the documented scope/deletion decision; no implementation is required unless scope changes.</v>
+      </c>
+    </row>
+    <row r="36" ht="156" customHeight="1">
       <c r="A36" s="5" t="n">
         <v>35</v>
       </c>
@@ -2992,8 +3670,18 @@
       <c r="K36" s="28" t="str">
         <v>Field MEDPAR-POA-DGNS-CD-CNT: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="37" ht="36" customHeight="1">
+      <c r="L36" s="64" t="str">
+        <v>Item: 35 — MEDPAR-POA-DGNS-CD-CNT
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-POA-DGNS-CD-CNT, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-POA-DGNS-CD-CNT (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Diag Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: 25 POA/diagnosis (12 E-code) limits, version code, blank POA.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="37" ht="156" customHeight="1">
       <c r="A37" s="5" t="n">
         <v>36</v>
       </c>
@@ -3041,8 +3729,18 @@
       <c r="K37" s="28" t="str">
         <v>Field MEDPAR-POA-DGNS-E-CD-CNT: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
+      <c r="L37" s="64" t="str">
+        <v>Item: 36 — MEDPAR-POA-DGNS-E-CD-CNT
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-POA-DGNS-E-CD-CNT, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-POA-DGNS-E-CD-CNT (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Diag Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: 25 POA/diagnosis (12 E-code) limits, version code, blank POA.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="38" ht="156" customHeight="1">
       <c r="A38" s="5" t="n">
         <v>37</v>
       </c>
@@ -3090,8 +3788,18 @@
       <c r="K38" s="28" t="str">
         <v>Field MEDPAR-POA-DGNS-E-IND-CD: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
+      <c r="L38" s="64" t="str">
+        <v>Item: 37 — MEDPAR-POA-DGNS-E-IND-CD
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-POA-DGNS-E-IND-CD, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-POA-DGNS-E-IND-CD (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Diag Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: 25 POA/diagnosis (12 E-code) limits, version code, blank POA.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="39" ht="156" customHeight="1">
       <c r="A39" s="5" t="n">
         <v>38</v>
       </c>
@@ -3139,8 +3847,18 @@
       <c r="K39" s="28" t="str">
         <v>Field MEDPAR-POA-DGNS-IND-CD: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
+      <c r="L39" s="64" t="str">
+        <v>Item: 38 — MEDPAR-POA-DGNS-IND-CD
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-POA-DGNS-IND-CD, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-POA-DGNS-IND-CD (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Diag Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: 25 POA/diagnosis (12 E-code) limits, version code, blank POA.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="40" ht="156" customHeight="1">
       <c r="A40" s="5" t="n">
         <v>39</v>
       </c>
@@ -3188,8 +3906,18 @@
       <c r="K40" s="28" t="str">
         <v>Field MEDPAR-PPS-IND-0120: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
+      <c r="L40" s="64" t="str">
+        <v>Item: 39 — MEDPAR-PPS-IND-0120
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-PPS-IND-0120, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PPS-IND-0120 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Provider Info group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Provider-number 3rd/4th position table: one case per branch.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="41" ht="156" customHeight="1">
       <c r="A41" s="5" t="n">
         <v>40</v>
       </c>
@@ -3237,8 +3965,18 @@
       <c r="K41" s="28" t="str">
         <v>Field MEDPAR-PPS-STD-VAL-AMT-1190: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
+      <c r="L41" s="64" t="str">
+        <v>Item: 40 — MEDPAR-PPS-STD-VAL-AMT-1190
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-PPS-STD-VAL-AMT-1190, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PPS-STD-VAL-AMT-1190 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="42" ht="156" customHeight="1">
       <c r="A42" s="5" t="n">
         <v>41</v>
       </c>
@@ -3286,8 +4024,18 @@
       <c r="K42" s="28" t="str">
         <v>Field MEDPAR-PR-REPL-LIFECYC-SW-0820: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
+      <c r="L42" s="64" t="str">
+        <v>Item: 41 — MEDPAR-PR-REPL-LIFECYC-SW-0820
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-PR-REPL-LIFECYC-SW-0820, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PR-REPL-LIFECYC-SW-0820 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Condition Codes and other group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Code present -&gt; Y, absent -&gt; N, multiple codes, wrong-case code.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="43" ht="156" customHeight="1">
       <c r="A43" s="5" t="n">
         <v>42</v>
       </c>
@@ -3335,8 +4083,18 @@
       <c r="K43" s="28" t="str">
         <v>Field MEDPAR-PR-REPL-RECALL-SW-0830: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
+      <c r="L43" s="64" t="str">
+        <v>Item: 42 — MEDPAR-PR-REPL-RECALL-SW-0830
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-PR-REPL-RECALL-SW-0830, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PR-REPL-RECALL-SW-0830 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Condition Codes and other group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Code present -&gt; Y, absent -&gt; N, multiple codes, wrong-case code.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="44" ht="156" customHeight="1">
       <c r="A44" s="5" t="n">
         <v>43</v>
       </c>
@@ -3384,8 +4142,18 @@
       <c r="K44" s="28" t="str">
         <v>Field MEDPAR-PROV-CODE-0137: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
+      <c r="L44" s="64" t="str">
+        <v>Item: 43 — MEDPAR-PROV-CODE-0137
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-PROV-CODE-0137, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PROV-CODE-0137 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Provider Info group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Provider-number 3rd/4th position table: one case per branch.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="45" ht="156" customHeight="1">
       <c r="A45" s="5" t="n">
         <v>44</v>
       </c>
@@ -3433,8 +4201,18 @@
       <c r="K45" s="28" t="str">
         <v>Field MEDPAR-PROVIDER-0130: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="46" ht="48" customHeight="1">
+      <c r="L45" s="64" t="str">
+        <v>Item: 44 — MEDPAR-PROVIDER-0130
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-PROVIDER-0130, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PROVIDER-0130 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Provider Info group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Provider-number 3rd/4th position table: one case per branch.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="46" ht="156" customHeight="1">
       <c r="A46" s="5" t="n">
         <v>45</v>
       </c>
@@ -3482,8 +4260,18 @@
       <c r="K46" s="28" t="str">
         <v>Field MEDPAR-PRVDR-BASE-FAC-CCN-1650: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
+      <c r="L46" s="64" t="str">
+        <v>Item: 45 — MEDPAR-PRVDR-BASE-FAC-CCN-1650
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-PRVDR-BASE-FAC-CCN-1650, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PRVDR-BASE-FAC-CCN-1650 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Provider Info group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Provider-number 3rd/4th position table: one case per branch.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="47" ht="156" customHeight="1">
       <c r="A47" s="5" t="n">
         <v>46</v>
       </c>
@@ -3531,8 +4319,18 @@
       <c r="K47" s="28" t="str">
         <v>Field MEDPAR-S-NTRL-PMT-CST-AMT-1290: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
+      <c r="L47" s="64" t="str">
+        <v>Item: 46 — MEDPAR-S-NTRL-PMT-CST-AMT-1290
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-S-NTRL-PMT-CST-AMT-1290, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-S-NTRL-PMT-CST-AMT-1290 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="48" ht="156" customHeight="1">
       <c r="A48" s="5" t="n">
         <v>47</v>
       </c>
@@ -3580,8 +4378,18 @@
       <c r="K48" s="28" t="str">
         <v>Field MEDPAR-S-NTRL-PMT-IPPS-AM-1300: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="49" ht="48" customHeight="1">
+      <c r="L48" s="64" t="str">
+        <v>Item: 47 — MEDPAR-S-NTRL-PMT-IPPS-AM-1300
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-S-NTRL-PMT-IPPS-AM-1300, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-S-NTRL-PMT-IPPS-AM-1300 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="49" ht="156" customHeight="1">
       <c r="A49" s="5" t="n">
         <v>48</v>
       </c>
@@ -3629,8 +4437,18 @@
       <c r="K49" s="28" t="str">
         <v>Field MEDPAR-SQSTRTN-RDCTN-AMT-1130: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
+      <c r="L49" s="64" t="str">
+        <v>Item: 48 — MEDPAR-SQSTRTN-RDCTN-AMT-1130
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-SQSTRTN-RDCTN-AMT-1130, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-SQSTRTN-RDCTN-AMT-1130 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="50" ht="156" customHeight="1">
       <c r="A50" s="5" t="n">
         <v>49</v>
       </c>
@@ -3678,8 +4496,18 @@
       <c r="K50" s="28" t="str">
         <v>Field MEDPAR-SS-LS-SNF-IND-0140: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
+      <c r="L50" s="64" t="str">
+        <v>Item: 49 — MEDPAR-SS-LS-SNF-IND-0140
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-SS-LS-SNF-IND-0140, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-SS-LS-SNF-IND-0140 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Populate SS/LS/SNF indicator group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive, negative and boundary case for the field.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="51" ht="156" customHeight="1">
       <c r="A51" s="5" t="n">
         <v>50</v>
       </c>
@@ -3727,8 +4555,18 @@
       <c r="K51" s="28" t="str">
         <v>Field MEDPAR-SSI-DATA-0251: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
+      <c r="L51" s="64" t="str">
+        <v>Item: 50 — MEDPAR-SSI-DATA-0251
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-SSI-DATA-0251, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-SSI-DATA-0251 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Calculate SSI Day Cnt group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: SSI days: month boundaries, benefits exhausted, inpatient only.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="52" ht="156" customHeight="1">
       <c r="A52" s="5" t="n">
         <v>51</v>
       </c>
@@ -3776,8 +4614,18 @@
       <c r="K52" s="28" t="str">
         <v>Field MEDPAR-SSI-DATA-0252: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="53" ht="36" customHeight="1">
+      <c r="L52" s="64" t="str">
+        <v>Item: 51 — MEDPAR-SSI-DATA-0252
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-SSI-DATA-0252, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-SSI-DATA-0252 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Calculate SSI Indicator group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: SSI days: month boundaries, benefits exhausted, inpatient only.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="53" ht="156" customHeight="1">
       <c r="A53" s="5" t="n">
         <v>52</v>
       </c>
@@ -3825,8 +4673,18 @@
       <c r="K53" s="28" t="str">
         <v>Field MEDPAR-SSI-DATA-0253: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="54" ht="36" customHeight="1">
+      <c r="L53" s="64" t="str">
+        <v>Item: 52 — MEDPAR-SSI-DATA-0253
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-SSI-DATA-0253, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-SSI-DATA-0253 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Calculate SSI Indicator group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: SSI days: month boundaries, benefits exhausted, inpatient only.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="54" ht="156" customHeight="1">
       <c r="A54" s="5" t="n">
         <v>53</v>
       </c>
@@ -3874,8 +4732,18 @@
       <c r="K54" s="28" t="str">
         <v>Field MEDPAR-SSO-STD-PMT-AMT-1320: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="55" ht="48" customHeight="1">
+      <c r="L54" s="64" t="str">
+        <v>Item: 53 — MEDPAR-SSO-STD-PMT-AMT-1320
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-SSO-STD-PMT-AMT-1320, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-SSO-STD-PMT-AMT-1320 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="55" ht="156" customHeight="1">
       <c r="A55" s="5" t="n">
         <v>54</v>
       </c>
@@ -3923,8 +4791,18 @@
       <c r="K55" s="28" t="str">
         <v>Field MEDPAR-UNCMP-CARE-PMT-AMT-1140: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="56" ht="48" customHeight="1">
+      <c r="L55" s="64" t="str">
+        <v>Item: 54 — MEDPAR-UNCMP-CARE-PMT-AMT-1140
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-UNCMP-CARE-PMT-AMT-1140, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-UNCMP-CARE-PMT-AMT-1140 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="56" ht="156" customHeight="1">
       <c r="A56" s="5" t="n">
         <v>55</v>
       </c>
@@ -3972,8 +4850,18 @@
       <c r="K56" s="28" t="str">
         <v>Field MEDPAR-VALQ1-PMT-RDCTN-AM-1470: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="57" ht="36" customHeight="1">
+      <c r="L56" s="64" t="str">
+        <v>Item: 55 — MEDPAR-VALQ1-PMT-RDCTN-AM-1470
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-VALQ1-PMT-RDCTN-AM-1470, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-VALQ1-PMT-RDCTN-AM-1470 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="57" ht="156" customHeight="1">
       <c r="A57" s="5" t="n">
         <v>56</v>
       </c>
@@ -4021,8 +4909,18 @@
       <c r="K57" s="28" t="str">
         <v>Field MEDPAR-VALQB-PMT-ADJ-AMT-1500: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="58" ht="36" customHeight="1">
+      <c r="L57" s="64" t="str">
+        <v>Item: 56 — MEDPAR-VALQB-PMT-ADJ-AMT-1500
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-VALQB-PMT-ADJ-AMT-1500, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-VALQB-PMT-ADJ-AMT-1500 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="58" ht="156" customHeight="1">
       <c r="A58" s="5" t="n">
         <v>57</v>
       </c>
@@ -4070,8 +4968,18 @@
       <c r="K58" s="28" t="str">
         <v>Field MEDPAR-VBP-ADJSTMT-AMT-1160: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="59" ht="36" customHeight="1">
+      <c r="L58" s="64" t="str">
+        <v>Item: 57 — MEDPAR-VBP-ADJSTMT-AMT-1160
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-VBP-ADJSTMT-AMT-1160, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-VBP-ADJSTMT-AMT-1160 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Value Codes derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Value code present/absent, several lines summed, rounding, overflow to all 9s.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="59" ht="156" customHeight="1">
       <c r="A59" s="5" t="n">
         <v>58</v>
       </c>
@@ -4119,8 +5027,18 @@
       <c r="K59" s="28" t="str">
         <v>Field MEDPAR-2-MIDNGHT-STAY-IND-1280: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="60" ht="48" customHeight="1">
+      <c r="L59" s="64" t="str">
+        <v>Item: 58 — MEDPAR-2-MIDNGHT-STAY-IND-1280
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-2-MIDNGHT-STAY-IND-1280, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-2-MIDNGHT-STAY-IND-1280 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the SPAN-CODE TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive, negative and boundary case for the field.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="60" ht="156" customHeight="1">
       <c r="A60" s="5" t="n">
         <v>59</v>
       </c>
@@ -4168,8 +5086,18 @@
       <c r="K60" s="28" t="str">
         <v>Field MEDPAR-ACCOMMODATION-CHRG-0460: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="61" ht="48" customHeight="1">
+      <c r="L60" s="64" t="str">
+        <v>Item: 59 — MEDPAR-ACCOMMODATION-CHRG-0460
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-ACCOMMODATION-CHRG-0460, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ACCOMMODATION-CHRG-0460 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="61" ht="156" customHeight="1">
       <c r="A61" s="5" t="n">
         <v>60</v>
       </c>
@@ -4217,8 +5145,18 @@
       <c r="K61" s="28" t="str">
         <v>Field MEDPAR-ACCOMMODATION-DAYS-0450: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="62" ht="36" customHeight="1">
+      <c r="L61" s="64" t="str">
+        <v>Item: 60 — MEDPAR-ACCOMMODATION-DAYS-0450
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-ACCOMMODATION-DAYS-0450, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ACCOMMODATION-DAYS-0450 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="62" ht="156" customHeight="1">
       <c r="A62" s="5" t="n">
         <v>61</v>
       </c>
@@ -4266,8 +5204,18 @@
       <c r="K62" s="28" t="str">
         <v>Field MEDPAR-ACCRETION-DATE-0160: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="63" ht="36" customHeight="1">
+      <c r="L62" s="64" t="str">
+        <v>Item: 61 — MEDPAR-ACCRETION-DATE-0160
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-ACCRETION-DATE-0160, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ACCRETION-DATE-0160 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the YYYYDDD group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Convert YYYYMMDD to Julian YYYYDDD: leap year, Dec 31, Jan 1; the date normaliser must accept it.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="63" ht="156" customHeight="1">
       <c r="A63" s="5" t="n">
         <v>62</v>
       </c>
@@ -4315,8 +5263,18 @@
       <c r="K63" s="28" t="str">
         <v>Field MEDPAR-ADM-DATE-0200: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="64" ht="36" customHeight="1">
+      <c r="L63" s="64" t="str">
+        <v>Item: 62 — MEDPAR-ADM-DATE-0200
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-ADM-DATE-0200, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ADM-DATE-0200 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the YYYYDDD group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Convert YYYYMMDD to Julian YYYYDDD: leap year, Dec 31, Jan 1; the date normaliser must accept it.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="64" ht="156" customHeight="1">
       <c r="A64" s="5" t="n">
         <v>63</v>
       </c>
@@ -4364,8 +5322,18 @@
       <c r="K64" s="28" t="str">
         <v>Field MEDPAR-ADM-DAY-0090: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="65" ht="36" customHeight="1">
+      <c r="L64" s="64" t="str">
+        <v>Item: 63 — MEDPAR-ADM-DAY-0090
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-ADM-DAY-0090, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ADM-DAY-0090 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the YYYYDDD group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Convert YYYYMMDD to Julian YYYYDDD: leap year, Dec 31, Jan 1; the date normaliser must accept it.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="65" ht="156" customHeight="1">
       <c r="A65" s="5" t="n">
         <v>64</v>
       </c>
@@ -4413,8 +5381,18 @@
       <c r="K65" s="28" t="str">
         <v>Field MEDPAR-ALGNC-STEM-CELLAMT-1440: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="66" ht="36" customHeight="1">
+      <c r="L65" s="64" t="str">
+        <v>Item: 64 — MEDPAR-ALGNC-STEM-CELLAMT-1440
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-ALGNC-STEM-CELLAMT-1440, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ALGNC-STEM-CELLAMT-1440 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="66" ht="156" customHeight="1">
       <c r="A66" s="5" t="n">
         <v>65</v>
       </c>
@@ -4462,8 +5440,18 @@
       <c r="K66" s="28" t="str">
         <v>Field MEDPAR-CELL-GENE-PRC-AMT-1510: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="67" ht="36" customHeight="1">
+      <c r="L66" s="64" t="str">
+        <v>Item: 65 — MEDPAR-CELL-GENE-PRC-AMT-1510
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-CELL-GENE-PRC-AMT-1510, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CELL-GENE-PRC-AMT-1510 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="67" ht="156" customHeight="1">
       <c r="A67" s="5" t="n">
         <v>66</v>
       </c>
@@ -4511,8 +5499,18 @@
       <c r="K67" s="28" t="str">
         <v>Field MEDPAR-CELL-TPY-DRUG-AMT-1520: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="68" ht="36" customHeight="1">
+      <c r="L67" s="64" t="str">
+        <v>Item: 66 — MEDPAR-CELL-TPY-DRUG-AMT-1520
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-CELL-TPY-DRUG-AMT-1520, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CELL-TPY-DRUG-AMT-1520 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="68" ht="168" customHeight="1">
       <c r="A68" s="5" t="n">
         <v>67</v>
       </c>
@@ -4560,8 +5558,18 @@
       <c r="K68" s="28" t="str">
         <v>Field MEDPAR-CORONARY-CARE-IND-0482: golden comparison and independent highest-accumulated-charge ICU/CCU type validation are implemented, with missing-charge/tie blocks. Evidence: intermediate/business_rules.py and test_gap_register_business_rules.py. Approved golden fixture/current byte offset still required.</v>
       </c>
-    </row>
-    <row r="69" ht="36" customHeight="1">
+      <c r="L68" s="64" t="str">
+        <v>Item: 67 — MEDPAR-CORONARY-CARE-IND-0482
+Completed: Golden comparison and independent highest-accumulated-charge ICU/CCU type validation, with missing-charge/tie blocks. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Partial: For MEDPAR-CORONARY-CARE-IND-0482, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture/current byte offset required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CORONARY-CARE-IND-0482 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="69" ht="156" customHeight="1">
       <c r="A69" s="5" t="n">
         <v>68</v>
       </c>
@@ -4609,8 +5617,18 @@
       <c r="K69" s="28" t="str">
         <v>Field MEDPAR-COV-CHRG-0410: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="70" ht="36" customHeight="1">
+      <c r="L69" s="64" t="str">
+        <v>Item: 68 — MEDPAR-COV-CHRG-0410
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-COV-CHRG-0410, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-COV-CHRG-0410 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="70" ht="156" customHeight="1">
       <c r="A70" s="5" t="n">
         <v>69</v>
       </c>
@@ -4658,8 +5676,18 @@
       <c r="K70" s="28" t="str">
         <v>Field MEDPAR-CRDC-CATHRZTN-AMT-1120: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="71" ht="36" customHeight="1">
+      <c r="L70" s="64" t="str">
+        <v>Item: 69 — MEDPAR-CRDC-CATHRZTN-AMT-1120
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-CRDC-CATHRZTN-AMT-1120, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CRDC-CATHRZTN-AMT-1120 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="71" ht="156" customHeight="1">
       <c r="A71" s="5" t="n">
         <v>70</v>
       </c>
@@ -4707,8 +5735,18 @@
       <c r="K71" s="28" t="str">
         <v>Field MEDPAR-DATE-BENFEX-0170: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="72" ht="36" customHeight="1">
+      <c r="L71" s="64" t="str">
+        <v>Item: 70 — MEDPAR-DATE-BENFEX-0170
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-DATE-BENFEX-0170, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-DATE-BENFEX-0170 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the YYYYDDD group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Convert YYYYMMDD to Julian YYYYDDD: leap year, Dec 31, Jan 1; the date normaliser must accept it.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="72" ht="156" customHeight="1">
       <c r="A72" s="5" t="n">
         <v>71</v>
       </c>
@@ -4756,8 +5794,18 @@
       <c r="K72" s="28" t="str">
         <v>Field MEDPAR-DISCHG-DATE-0210: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="73" ht="36" customHeight="1">
+      <c r="L72" s="64" t="str">
+        <v>Item: 71 — MEDPAR-DISCHG-DATE-0210
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-DISCHG-DATE-0210, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-DISCHG-DATE-0210 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the YYYYDDD group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Convert YYYYMMDD to Julian YYYYDDD: leap year, Dec 31, Jan 1; the date normaliser must accept it.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="73" ht="156" customHeight="1">
       <c r="A73" s="5" t="n">
         <v>72</v>
       </c>
@@ -4805,8 +5853,18 @@
       <c r="K73" s="28" t="str">
         <v>Field MEDPAR-DTE-CR-ENDED-0220: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="74" ht="36" customHeight="1">
+      <c r="L73" s="64" t="str">
+        <v>Item: 72 — MEDPAR-DTE-CR-ENDED-0220
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-DTE-CR-ENDED-0220, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-DTE-CR-ENDED-0220 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the YYYYDDD group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Convert YYYYMMDD to Julian YYYYDDD: leap year, Dec 31, Jan 1; the date normaliser must accept it.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="74" ht="156" customHeight="1">
       <c r="A74" s="5" t="n">
         <v>73</v>
       </c>
@@ -4854,8 +5912,18 @@
       <c r="K74" s="28" t="str">
         <v>Field MEDPAR-ESRD-SETTING-IND-0488: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="75" ht="36" customHeight="1">
+      <c r="L74" s="64" t="str">
+        <v>Item: 73 — MEDPAR-ESRD-SETTING-IND-0488
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-ESRD-SETTING-IND-0488, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ESRD-SETTING-IND-0488 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="75" ht="156" customHeight="1">
       <c r="A75" s="5" t="n">
         <v>74</v>
       </c>
@@ -4903,8 +5971,18 @@
       <c r="K75" s="28" t="str">
         <v>Field MEDPAR-GENE-TPY-DRUG-AMT-1530: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="76" ht="36" customHeight="1">
+      <c r="L75" s="64" t="str">
+        <v>Item: 74 — MEDPAR-GENE-TPY-DRUG-AMT-1530
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-GENE-TPY-DRUG-AMT-1530, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-GENE-TPY-DRUG-AMT-1530 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="76" ht="156" customHeight="1">
       <c r="A76" s="5" t="n">
         <v>75</v>
       </c>
@@ -4952,8 +6030,18 @@
       <c r="K76" s="28" t="str">
         <v>Field MEDPAR-HOSP-HOME-CHRG-AMT-1620: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="77" ht="48" customHeight="1">
+      <c r="L76" s="64" t="str">
+        <v>Item: 75 — MEDPAR-HOSP-HOME-CHRG-AMT-1620
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-HOSP-HOME-CHRG-AMT-1620, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-HOSP-HOME-CHRG-AMT-1620 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="77" ht="156" customHeight="1">
       <c r="A77" s="5" t="n">
         <v>76</v>
       </c>
@@ -5001,8 +6089,18 @@
       <c r="K77" s="28" t="str">
         <v>Field MEDPAR-HOSP-HOME-FROM-DT-1630: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="78" ht="48" customHeight="1">
+      <c r="L77" s="64" t="str">
+        <v>Item: 76 — MEDPAR-HOSP-HOME-FROM-DT-1630
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-HOSP-HOME-FROM-DT-1630, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-HOSP-HOME-FROM-DT-1630 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the SPAN-CODE TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive, negative and boundary case for the field.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="78" ht="156" customHeight="1">
       <c r="A78" s="5" t="n">
         <v>77</v>
       </c>
@@ -5050,8 +6148,18 @@
       <c r="K78" s="28" t="str">
         <v>Field MEDPAR-HOSP-HOME-THRU-DT-1640: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="79" ht="36" customHeight="1">
+      <c r="L78" s="64" t="str">
+        <v>Item: 77 — MEDPAR-HOSP-HOME-THRU-DT-1640
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-HOSP-HOME-THRU-DT-1640, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-HOSP-HOME-THRU-DT-1640 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the SPAN-CODE TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive, negative and boundary case for the field.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="79" ht="156" customHeight="1">
       <c r="A79" s="5" t="n">
         <v>78</v>
       </c>
@@ -5099,8 +6207,18 @@
       <c r="K79" s="28" t="str">
         <v>Field MEDPAR-INCDNT-DGN-SRV-AMT-1000: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="80" ht="36" customHeight="1">
+      <c r="L79" s="64" t="str">
+        <v>Item: 78 — MEDPAR-INCDNT-DGN-SRV-AMT-1000
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-INCDNT-DGN-SRV-AMT-1000, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-INCDNT-DGN-SRV-AMT-1000 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="80" ht="156" customHeight="1">
       <c r="A80" s="5" t="n">
         <v>79</v>
       </c>
@@ -5148,8 +6266,18 @@
       <c r="K80" s="28" t="str">
         <v>Field MEDPAR-INCDNT-RDLGY-AMT-0990: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="81" ht="36" customHeight="1">
+      <c r="L80" s="64" t="str">
+        <v>Item: 79 — MEDPAR-INCDNT-RDLGY-AMT-0990
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-INCDNT-RDLGY-AMT-0990, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-INCDNT-RDLGY-AMT-0990 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="81" ht="168" customHeight="1">
       <c r="A81" s="5" t="n">
         <v>80</v>
       </c>
@@ -5197,8 +6325,18 @@
       <c r="K81" s="28" t="str">
         <v>Field MEDPAR-INTERSIVE-CARE-IND-0481: golden comparison and independent highest-accumulated-charge ICU/CCU type validation are implemented, with missing-charge/tie blocks. Evidence: intermediate/business_rules.py and test_gap_register_business_rules.py. Approved golden fixture/current byte offset still required.</v>
       </c>
-    </row>
-    <row r="82" ht="36" customHeight="1">
+      <c r="L81" s="64" t="str">
+        <v>Item: 80 — MEDPAR-INTERSIVE-CARE-IND-0481
+Completed: Golden comparison and independent highest-accumulated-charge ICU/CCU type validation, with missing-charge/tie blocks. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Partial: For MEDPAR-INTERSIVE-CARE-IND-0481, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture/current byte offset required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-INTERSIVE-CARE-IND-0481 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="82" ht="156" customHeight="1">
       <c r="A82" s="5" t="n">
         <v>81</v>
       </c>
@@ -5246,8 +6384,18 @@
       <c r="K82" s="28" t="str">
         <v>Field MEDPAR-INTRAOCULAR-LN-AMT-0950: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="83" ht="36" customHeight="1">
+      <c r="L82" s="64" t="str">
+        <v>Item: 81 — MEDPAR-INTRAOCULAR-LN-AMT-0950
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-INTRAOCULAR-LN-AMT-0950, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-INTRAOCULAR-LN-AMT-0950 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="83" ht="156" customHeight="1">
       <c r="A83" s="5" t="n">
         <v>82</v>
       </c>
@@ -5295,8 +6443,18 @@
       <c r="K83" s="28" t="str">
         <v>Field MEDPAR-INVSTGTNL-DVC-AMT-1020: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="84" ht="36" customHeight="1">
+      <c r="L83" s="64" t="str">
+        <v>Item: 82 — MEDPAR-INVSTGTNL-DVC-AMT-1020
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-INVSTGTNL-DVC-AMT-1020, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-INVSTGTNL-DVC-AMT-1020 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="84" ht="156" customHeight="1">
       <c r="A84" s="5" t="n">
         <v>83</v>
       </c>
@@ -5344,8 +6502,18 @@
       <c r="K84" s="28" t="str">
         <v>Field MEDPAR-MDCL-SRG-DRSNG-AMT-1010: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="85" ht="36" customHeight="1">
+      <c r="L84" s="64" t="str">
+        <v>Item: 83 — MEDPAR-MDCL-SRG-DRSNG-AMT-1010
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-MDCL-SRG-DRSNG-AMT-1010, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-MDCL-SRG-DRSNG-AMT-1010 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="85" ht="156" customHeight="1">
       <c r="A85" s="5" t="n">
         <v>84</v>
       </c>
@@ -5393,8 +6561,18 @@
       <c r="K85" s="28" t="str">
         <v>Field MEDPAR-MDCL-SRG-GEN-AMT-0890: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="86" ht="36" customHeight="1">
+      <c r="L85" s="64" t="str">
+        <v>Item: 84 — MEDPAR-MDCL-SRG-GEN-AMT-0890
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-MDCL-SRG-GEN-AMT-0890, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-MDCL-SRG-GEN-AMT-0890 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="86" ht="156" customHeight="1">
       <c r="A86" s="5" t="n">
         <v>85</v>
       </c>
@@ -5442,8 +6620,18 @@
       <c r="K86" s="28" t="str">
         <v>Field MEDPAR-MDCL-SRG-NSTRL-AMT-0900: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="87" ht="36" customHeight="1">
+      <c r="L86" s="64" t="str">
+        <v>Item: 85 — MEDPAR-MDCL-SRG-NSTRL-AMT-0900
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-MDCL-SRG-NSTRL-AMT-0900, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-MDCL-SRG-NSTRL-AMT-0900 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="87" ht="156" customHeight="1">
       <c r="A87" s="5" t="n">
         <v>86</v>
       </c>
@@ -5491,8 +6679,18 @@
       <c r="K87" s="28" t="str">
         <v>Field MEDPAR-MDCL-SRG-PCMKR-AMT-0940: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="88" ht="36" customHeight="1">
+      <c r="L87" s="64" t="str">
+        <v>Item: 86 — MEDPAR-MDCL-SRG-PCMKR-AMT-0940
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-MDCL-SRG-PCMKR-AMT-0940, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-MDCL-SRG-PCMKR-AMT-0940 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="88" ht="156" customHeight="1">
       <c r="A88" s="5" t="n">
         <v>87</v>
       </c>
@@ -5540,8 +6738,18 @@
       <c r="K88" s="28" t="str">
         <v>Field MEDPAR-MDCL-SRG-STRL-AMT-0910: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="89" ht="36" customHeight="1">
+      <c r="L88" s="64" t="str">
+        <v>Item: 87 — MEDPAR-MDCL-SRG-STRL-AMT-0910
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-MDCL-SRG-STRL-AMT-0910, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-MDCL-SRG-STRL-AMT-0910 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="89" ht="156" customHeight="1">
       <c r="A89" s="5" t="n">
         <v>88</v>
       </c>
@@ -5589,8 +6797,18 @@
       <c r="K89" s="28" t="str">
         <v>Field MEDPAR-MDCL-SRG-TKHME-AMT-0920: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="90" ht="36" customHeight="1">
+      <c r="L89" s="64" t="str">
+        <v>Item: 88 — MEDPAR-MDCL-SRG-TKHME-AMT-0920
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-MDCL-SRG-TKHME-AMT-0920, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-MDCL-SRG-TKHME-AMT-0920 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="90" ht="156" customHeight="1">
       <c r="A90" s="5" t="n">
         <v>89</v>
       </c>
@@ -5638,8 +6856,18 @@
       <c r="K90" s="28" t="str">
         <v>Field MEDPAR-MDCL-SRGL-MISC-AMT-1030: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="91" ht="36" customHeight="1">
+      <c r="L90" s="64" t="str">
+        <v>Item: 89 — MEDPAR-MDCL-SRGL-MISC-AMT-1030
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-MDCL-SRGL-MISC-AMT-1030, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-MDCL-SRGL-MISC-AMT-1030 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="91" ht="156" customHeight="1">
       <c r="A91" s="5" t="n">
         <v>90</v>
       </c>
@@ -5687,8 +6915,18 @@
       <c r="K91" s="28" t="str">
         <v>Field MEDPAR-OBSRVTN-SW-0850: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="92" ht="36" customHeight="1">
+      <c r="L91" s="64" t="str">
+        <v>Item: 90 — MEDPAR-OBSRVTN-SW-0850
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-OBSRVTN-SW-0850, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-OBSRVTN-SW-0850 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="92" ht="156" customHeight="1">
       <c r="A92" s="5" t="n">
         <v>91</v>
       </c>
@@ -5736,8 +6974,18 @@
       <c r="K92" s="28" t="str">
         <v>Field MEDPAR-OPRTG-ROOM-AMT-1100: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="93" ht="36" customHeight="1">
+      <c r="L92" s="64" t="str">
+        <v>Item: 91 — MEDPAR-OPRTG-ROOM-AMT-1100
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-OPRTG-ROOM-AMT-1100, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-OPRTG-ROOM-AMT-1100 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="93" ht="156" customHeight="1">
       <c r="A93" s="5" t="n">
         <v>92</v>
       </c>
@@ -5785,8 +7033,18 @@
       <c r="K93" s="28" t="str">
         <v>Field MEDPAR-OR-LABOR-DLVRY-AMT-1110: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="94" ht="36" customHeight="1">
+      <c r="L93" s="64" t="str">
+        <v>Item: 92 — MEDPAR-OR-LABOR-DLVRY-AMT-1110
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-OR-LABOR-DLVRY-AMT-1110, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-OR-LABOR-DLVRY-AMT-1110 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="94" ht="156" customHeight="1">
       <c r="A94" s="5" t="n">
         <v>93</v>
       </c>
@@ -5834,8 +7092,18 @@
       <c r="K94" s="28" t="str">
         <v>Field MEDPAR-ORGAN-IND-0487: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="95" ht="36" customHeight="1">
+      <c r="L94" s="64" t="str">
+        <v>Item: 93 — MEDPAR-ORGAN-IND-0487
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-ORGAN-IND-0487, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ORGAN-IND-0487 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="95" ht="156" customHeight="1">
       <c r="A95" s="5" t="n">
         <v>94</v>
       </c>
@@ -5883,8 +7151,18 @@
       <c r="K95" s="28" t="str">
         <v>Field MEDPAR-OTHR-IMPLANTS-AMT-0970: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="96" ht="36" customHeight="1">
+      <c r="L95" s="64" t="str">
+        <v>Item: 94 — MEDPAR-OTHR-IMPLANTS-AMT-0970
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-OTHR-IMPLANTS-AMT-0970, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-OTHR-IMPLANTS-AMT-0970 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="96" ht="156" customHeight="1">
       <c r="A96" s="5" t="n">
         <v>95</v>
       </c>
@@ -5932,8 +7210,18 @@
       <c r="K96" s="28" t="str">
         <v>Field MEDPAR-OTHR-SUPPL-DVC-AMT-0980: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="97" ht="36" customHeight="1">
+      <c r="L96" s="64" t="str">
+        <v>Item: 95 — MEDPAR-OTHR-SUPPL-DVC-AMT-0980
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-OTHR-SUPPL-DVC-AMT-0980, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-OTHR-SUPPL-DVC-AMT-0980 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="97" ht="156" customHeight="1">
       <c r="A97" s="5" t="n">
         <v>96</v>
       </c>
@@ -5981,8 +7269,18 @@
       <c r="K97" s="28" t="str">
         <v>Field MEDPAR-OUTPATIENT-SRV-IND-0486: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="98" ht="36" customHeight="1">
+      <c r="L97" s="64" t="str">
+        <v>Item: 96 — MEDPAR-OUTPATIENT-SRV-IND-0486
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-OUTPATIENT-SRV-IND-0486, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-OUTPATIENT-SRV-IND-0486 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="98" ht="156" customHeight="1">
       <c r="A98" s="5" t="n">
         <v>97</v>
       </c>
@@ -6030,8 +7328,18 @@
       <c r="K98" s="28" t="str">
         <v>Field MEDPAR-OXYGN-TKEHOME-AMT-0960: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="99" ht="36" customHeight="1">
+      <c r="L98" s="64" t="str">
+        <v>Item: 97 — MEDPAR-OXYGN-TKEHOME-AMT-0960
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-OXYGN-TKEHOME-AMT-0960, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-OXYGN-TKEHOME-AMT-0960 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="99" ht="156" customHeight="1">
       <c r="A99" s="5" t="n">
         <v>98</v>
       </c>
@@ -6079,8 +7387,18 @@
       <c r="K99" s="28" t="str">
         <v>Field MEDPAR-PHARMACY-IND-0483: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="100" ht="36" customHeight="1">
+      <c r="L99" s="64" t="str">
+        <v>Item: 98 — MEDPAR-PHARMACY-IND-0483
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-PHARMACY-IND-0483, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PHARMACY-IND-0483 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="100" ht="156" customHeight="1">
       <c r="A100" s="5" t="n">
         <v>99</v>
       </c>
@@ -6128,8 +7446,18 @@
       <c r="K100" s="28" t="str">
         <v>Field MEDPAR-PRSTHTC-ORTHTC-AMT-0930: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="101" ht="36" customHeight="1">
+      <c r="L100" s="64" t="str">
+        <v>Item: 99 — MEDPAR-PRSTHTC-ORTHTC-AMT-0930
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-PRSTHTC-ORTHTC-AMT-0930, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PRSTHTC-ORTHTC-AMT-0930 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="101" ht="156" customHeight="1">
       <c r="A101" s="5" t="n">
         <v>100</v>
       </c>
@@ -6177,8 +7505,18 @@
       <c r="K101" s="28" t="str">
         <v>Field MEDPAR-PTNT-ADD-ON-AMT-1230: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="102" ht="36" customHeight="1">
+      <c r="L101" s="64" t="str">
+        <v>Item: 100 — MEDPAR-PTNT-ADD-ON-AMT-1230
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-PTNT-ADD-ON-AMT-1230, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PTNT-ADD-ON-AMT-1230 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Multi Bill group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Multi-bill accumulation and first/last bill selection.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="102" ht="156" customHeight="1">
       <c r="A102" s="5" t="n">
         <v>101</v>
       </c>
@@ -6226,8 +7564,18 @@
       <c r="K102" s="28" t="str">
         <v>Field MEDPAR-RADIOLOGY-IND-O485: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="103" ht="36" customHeight="1">
+      <c r="L102" s="64" t="str">
+        <v>Item: 101 — MEDPAR-RADIOLOGY-IND-O485
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-RADIOLOGY-IND-O485, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-RADIOLOGY-IND-O485 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="103" ht="156" customHeight="1">
       <c r="A103" s="5" t="n">
         <v>102</v>
       </c>
@@ -6275,8 +7623,18 @@
       <c r="K103" s="28" t="str">
         <v>Field MEDPAR-RDLGY-CT-SCAN-AMT-1080: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="104" ht="36" customHeight="1">
+      <c r="L103" s="64" t="str">
+        <v>Item: 102 — MEDPAR-RDLGY-CT-SCAN-AMT-1080
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-RDLGY-CT-SCAN-AMT-1080, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-RDLGY-CT-SCAN-AMT-1080 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="104" ht="156" customHeight="1">
       <c r="A104" s="5" t="n">
         <v>103</v>
       </c>
@@ -6324,8 +7682,18 @@
       <c r="K104" s="28" t="str">
         <v>Field MEDPAR-RDLGY-DGNSTC-AMT-1050: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="105" ht="36" customHeight="1">
+      <c r="L104" s="64" t="str">
+        <v>Item: 103 — MEDPAR-RDLGY-DGNSTC-AMT-1050
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-RDLGY-DGNSTC-AMT-1050, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-RDLGY-DGNSTC-AMT-1050 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="105" ht="156" customHeight="1">
       <c r="A105" s="5" t="n">
         <v>104</v>
       </c>
@@ -6373,8 +7741,18 @@
       <c r="K105" s="28" t="str">
         <v>Field MEDPAR-RDLGY-NUCLR-MD-AMT-1070: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="106" ht="36" customHeight="1">
+      <c r="L105" s="64" t="str">
+        <v>Item: 104 — MEDPAR-RDLGY-NUCLR-MD-AMT-1070
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-RDLGY-NUCLR-MD-AMT-1070, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-RDLGY-NUCLR-MD-AMT-1070 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="106" ht="156" customHeight="1">
       <c r="A106" s="5" t="n">
         <v>105</v>
       </c>
@@ -6422,8 +7800,18 @@
       <c r="K106" s="28" t="str">
         <v>Field MEDPAR-RDLGY-ONCOLOGY-AMT-1040: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="107" ht="36" customHeight="1">
+      <c r="L106" s="64" t="str">
+        <v>Item: 105 — MEDPAR-RDLGY-ONCOLOGY-AMT-1040
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-RDLGY-ONCOLOGY-AMT-1040, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-RDLGY-ONCOLOGY-AMT-1040 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="107" ht="156" customHeight="1">
       <c r="A107" s="5" t="n">
         <v>106</v>
       </c>
@@ -6471,8 +7859,18 @@
       <c r="K107" s="28" t="str">
         <v>Field MEDPAR-RDLGY-OTHR-IMG-AMT-1090: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="108" ht="36" customHeight="1">
+      <c r="L107" s="64" t="str">
+        <v>Item: 106 — MEDPAR-RDLGY-OTHR-IMG-AMT-1090
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-RDLGY-OTHR-IMG-AMT-1090, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-RDLGY-OTHR-IMG-AMT-1090 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="108" ht="156" customHeight="1">
       <c r="A108" s="5" t="n">
         <v>107</v>
       </c>
@@ -6520,8 +7918,18 @@
       <c r="K108" s="28" t="str">
         <v>Field MEDPAR-RDLGY-THRPTC-AMT-1060: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="109" ht="36" customHeight="1">
+      <c r="L108" s="64" t="str">
+        <v>Item: 107 — MEDPAR-RDLGY-THRPTC-AMT-1060
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-RDLGY-THRPTC-AMT-1060, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-RDLGY-THRPTC-AMT-1060 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Totals group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Revenue-code group boundaries (first, last, just outside), multi-bill accumulation, overflow.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="109" ht="156" customHeight="1">
       <c r="A109" s="5" t="n">
         <v>108</v>
       </c>
@@ -6569,8 +7977,18 @@
       <c r="K109" s="28" t="str">
         <v>Field MEDPAR-REV-CNTR-MODL-AMT-1490: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="110" ht="36" customHeight="1">
+      <c r="L109" s="64" t="str">
+        <v>Item: 108 — MEDPAR-REV-CNTR-MODL-AMT-1490
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-REV-CNTR-MODL-AMT-1490, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-REV-CNTR-MODL-AMT-1490 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Multi Bill group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Multi-bill accumulation and first/last bill selection.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="110" ht="156" customHeight="1">
       <c r="A110" s="5" t="n">
         <v>109</v>
       </c>
@@ -6618,8 +8036,18 @@
       <c r="K110" s="28" t="str">
         <v>Field MEDPAR-REV-CNTR-NDC-NUM-1550: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="111" ht="36" customHeight="1">
+      <c r="L110" s="64" t="str">
+        <v>Item: 109 — MEDPAR-REV-CNTR-NDC-NUM-1550
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-REV-CNTR-NDC-NUM-1550, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-REV-CNTR-NDC-NUM-1550 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Multi Bill group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Multi-bill accumulation and first/last bill selection.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="111" ht="156" customHeight="1">
       <c r="A111" s="5" t="n">
         <v>110</v>
       </c>
@@ -6667,8 +8095,18 @@
       <c r="K111" s="28" t="str">
         <v>Field MEDPAR-REV-CNTR-RP-IND-CD-1400: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="112" ht="36" customHeight="1">
+      <c r="L111" s="64" t="str">
+        <v>Item: 110 — MEDPAR-REV-CNTR-RP-IND-CD-1400
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-REV-CNTR-RP-IND-CD-1400, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-REV-CNTR-RP-IND-CD-1400 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR Multi Bill group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Multi-bill accumulation and first/last bill selection.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="112" ht="156" customHeight="1">
       <c r="A112" s="5" t="n">
         <v>111</v>
       </c>
@@ -6716,8 +8154,18 @@
       <c r="K112" s="28" t="str">
         <v>Field MEDPAR-SERVICE-CHARGES-0470: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="113" ht="36" customHeight="1">
+      <c r="L112" s="64" t="str">
+        <v>Item: 111 — MEDPAR-SERVICE-CHARGES-0470
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-SERVICE-CHARGES-0470, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-SERVICE-CHARGES-0470 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="113" ht="156" customHeight="1">
       <c r="A113" s="5" t="n">
         <v>112</v>
       </c>
@@ -6765,8 +8213,18 @@
       <c r="K113" s="28" t="str">
         <v>Field MEDPAR-SNF-QUAL-FROM-DATE-0180: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="114" ht="36" customHeight="1">
+      <c r="L113" s="64" t="str">
+        <v>Item: 112 — MEDPAR-SNF-QUAL-FROM-DATE-0180
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-SNF-QUAL-FROM-DATE-0180, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-SNF-QUAL-FROM-DATE-0180 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the SPAN-CODE TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive, negative and boundary case for the field.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="114" ht="156" customHeight="1">
       <c r="A114" s="5" t="n">
         <v>113</v>
       </c>
@@ -6814,8 +8272,18 @@
       <c r="K114" s="28" t="str">
         <v>Field MEDPAR-SNF-QUAL-THRU-DATE-0190: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="115" ht="36" customHeight="1">
+      <c r="L114" s="64" t="str">
+        <v>Item: 113 — MEDPAR-SNF-QUAL-THRU-DATE-0190
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-SNF-QUAL-THRU-DATE-0190, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-SNF-QUAL-THRU-DATE-0190 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the SPAN-CODE TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive, negative and boundary case for the field.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="115" ht="156" customHeight="1">
       <c r="A115" s="5" t="n">
         <v>114</v>
       </c>
@@ -6863,8 +8331,18 @@
       <c r="K115" s="28" t="str">
         <v>Field MEDPAR-TOT-ACC-CHRG-0430: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="116" ht="36" customHeight="1">
+      <c r="L115" s="64" t="str">
+        <v>Item: 114 — MEDPAR-TOT-ACC-CHRG-0430
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-TOT-ACC-CHRG-0430, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-TOT-ACC-CHRG-0430 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="116" ht="156" customHeight="1">
       <c r="A116" s="5" t="n">
         <v>115</v>
       </c>
@@ -6912,8 +8390,18 @@
       <c r="K116" s="28" t="str">
         <v>Field MEDPAR-TOT-DPT-CHRG-0440: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="117" ht="36" customHeight="1">
+      <c r="L116" s="64" t="str">
+        <v>Item: 115 — MEDPAR-TOT-DPT-CHRG-0440
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-TOT-DPT-CHRG-0440, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-TOT-DPT-CHRG-0440 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="117" ht="156" customHeight="1">
       <c r="A117" s="5" t="n">
         <v>116</v>
       </c>
@@ -6961,8 +8449,18 @@
       <c r="K117" s="28" t="str">
         <v>Field MEDPAR-TRANSPLANT-IND-0484: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="118" ht="36" customHeight="1">
+      <c r="L117" s="64" t="str">
+        <v>Item: 116 — MEDPAR-TRANSPLANT-IND-0484
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-TRANSPLANT-IND-0484, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-TRANSPLANT-IND-0484 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the REV-CNTR TRAILER derivations group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Indicator set/unset for each revenue code range; boundary codes.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="118" ht="156" customHeight="1">
       <c r="A118" s="5" t="n">
         <v>117</v>
       </c>
@@ -7010,8 +8508,18 @@
       <c r="K118" s="28" t="str">
         <v>Field MED-DISCH-DEST-0532: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="119" ht="36" customHeight="1">
+      <c r="L118" s="64" t="str">
+        <v>Item: 117 — MED-DISCH-DEST-0532
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MED-DISCH-DEST-0532, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MED-DISCH-DEST-0532 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="119" ht="156" customHeight="1">
       <c r="A119" s="5" t="n">
         <v>118</v>
       </c>
@@ -7059,8 +8567,18 @@
       <c r="K119" s="28" t="str">
         <v>Field MED-OLD-BIC-0530: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="120" ht="36" customHeight="1">
+      <c r="L119" s="64" t="str">
+        <v>Item: 118 — MED-OLD-BIC-0530
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MED-OLD-BIC-0530, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MED-OLD-BIC-0530 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="120" ht="156" customHeight="1">
       <c r="A120" s="5" t="n">
         <v>119</v>
       </c>
@@ -7108,8 +8626,18 @@
       <c r="K120" s="28" t="str">
         <v>Field MED-OUTLIER-CODE-0533: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="121" ht="36" customHeight="1">
+      <c r="L120" s="64" t="str">
+        <v>Item: 119 — MED-OUTLIER-CODE-0533
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MED-OUTLIER-CODE-0533, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MED-OUTLIER-CODE-0533 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="121" ht="156" customHeight="1">
       <c r="A121" s="5" t="n">
         <v>120</v>
       </c>
@@ -7157,8 +8685,18 @@
       <c r="K121" s="28" t="str">
         <v>Field MEDPAR-ACO-ID-NUM-1410: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="122" ht="36" customHeight="1">
+      <c r="L121" s="64" t="str">
+        <v>Item: 120 — MEDPAR-ACO-ID-NUM-1410
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-ACO-ID-NUM-1410, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ACO-ID-NUM-1410 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="122" ht="156" customHeight="1">
       <c r="A122" s="5" t="n">
         <v>121</v>
       </c>
@@ -7206,8 +8744,18 @@
       <c r="K122" s="28" t="str">
         <v>Field MEDPAR-ADM-DIAG-CODE-0590: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="123" ht="36" customHeight="1">
+      <c r="L122" s="64" t="str">
+        <v>Item: 121 — MEDPAR-ADM-DIAG-CODE-0590
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-ADM-DIAG-CODE-0590, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ADM-DIAG-CODE-0590 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="123" ht="156" customHeight="1">
       <c r="A123" s="5" t="n">
         <v>122</v>
       </c>
@@ -7255,8 +8803,18 @@
       <c r="K123" s="28" t="str">
         <v>Field MEDPAR-ADM-SOURCE-0560: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="124" ht="36" customHeight="1">
+      <c r="L123" s="64" t="str">
+        <v>Item: 122 — MEDPAR-ADM-SOURCE-0560
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-ADM-SOURCE-0560, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ADM-SOURCE-0560 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="124" ht="156" customHeight="1">
       <c r="A124" s="5" t="n">
         <v>123</v>
       </c>
@@ -7304,8 +8862,18 @@
       <c r="K124" s="28" t="str">
         <v>Field MEDPAR-ADMTG-DGNS-VRSN-CD: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="125" ht="36" customHeight="1">
+      <c r="L124" s="64" t="str">
+        <v>Item: 123 — MEDPAR-ADMTG-DGNS-VRSN-CD
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-ADMTG-DGNS-VRSN-CD, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ADMTG-DGNS-VRSN-CD (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="125" ht="156" customHeight="1">
       <c r="A125" s="5" t="n">
         <v>124</v>
       </c>
@@ -7353,8 +8921,18 @@
       <c r="K125" s="28" t="str">
         <v>Field MEDPAR-AGE-0030: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="126" ht="36" customHeight="1">
+      <c r="L125" s="64" t="str">
+        <v>Item: 124 — MEDPAR-AGE-0030
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-AGE-0030, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-AGE-0030 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="126" ht="156" customHeight="1">
       <c r="A126" s="5" t="n">
         <v>125</v>
       </c>
@@ -7402,8 +8980,18 @@
       <c r="K126" s="28" t="str">
         <v>Field MEDPAR-AMT-REIMB-0420: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="127" ht="36" customHeight="1">
+      <c r="L126" s="64" t="str">
+        <v>Item: 125 — MEDPAR-AMT-REIMB-0420
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-AMT-REIMB-0420, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-AMT-REIMB-0420 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the float to integer group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Rounding boundary (x.499 / x.500) and integer storage; confirm the rounding rule (3 decimals vs whole number).
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="127" ht="156" customHeight="1">
       <c r="A127" s="5" t="n">
         <v>126</v>
       </c>
@@ -7451,8 +9039,18 @@
       <c r="K127" s="28" t="str">
         <v>Field MEDPAR-AT-PHYS-0650: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="128" ht="36" customHeight="1">
+      <c r="L127" s="64" t="str">
+        <v>Item: 126 — MEDPAR-AT-PHYS-0650
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-AT-PHYS-0650, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-AT-PHYS-0650 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="128" ht="156" customHeight="1">
       <c r="A128" s="5" t="n">
         <v>127</v>
       </c>
@@ -7500,8 +9098,18 @@
       <c r="K128" s="28" t="str">
         <v>Field MEDPAR-BENE-COUN-0072: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="129" ht="36" customHeight="1">
+      <c r="L128" s="64" t="str">
+        <v>Item: 127 — MEDPAR-BENE-COUN-0072
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-BENE-COUN-0072, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-BENE-COUN-0072 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="129" ht="156" customHeight="1">
       <c r="A129" s="5" t="n">
         <v>128</v>
       </c>
@@ -7549,8 +9157,18 @@
       <c r="K129" s="28" t="str">
         <v>Field MEDPAR-BENE-ST-0071: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="130" ht="36" customHeight="1">
+      <c r="L129" s="64" t="str">
+        <v>Item: 128 — MEDPAR-BENE-ST-0071
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-BENE-ST-0071, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-BENE-ST-0071 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="130" ht="156" customHeight="1">
       <c r="A130" s="5" t="n">
         <v>129</v>
       </c>
@@ -7598,8 +9216,18 @@
       <c r="K130" s="28" t="str">
         <v>Field MEDPAR-BIC-CODE-0022: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="131" ht="36" customHeight="1">
+      <c r="L130" s="64" t="str">
+        <v>Item: 129 — MEDPAR-BIC-CODE-0022
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-BIC-CODE-0022, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-BIC-CODE-0022 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="131" ht="156" customHeight="1">
       <c r="A131" s="5" t="n">
         <v>130</v>
       </c>
@@ -7647,8 +9275,18 @@
       <c r="K131" s="28" t="str">
         <v>Field MEDPAR-BILL-TOT-PERDIEM-0381: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="132" ht="36" customHeight="1">
+      <c r="L131" s="64" t="str">
+        <v>Item: 130 — MEDPAR-BILL-TOT-PERDIEM-0381
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-BILL-TOT-PERDIEM-0381, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-BILL-TOT-PERDIEM-0381 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the float to integer group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Rounding boundary (x.499 / x.500) and integer storage; confirm the rounding rule (3 decimals vs whole number).
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="132" ht="156" customHeight="1">
       <c r="A132" s="5" t="n">
         <v>131</v>
       </c>
@@ -7696,8 +9334,18 @@
       <c r="K132" s="28" t="str">
         <v>Field MEDPAR-BLOOD-DED-0330: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="133" ht="36" customHeight="1">
+      <c r="L132" s="64" t="str">
+        <v>Item: 131 — MEDPAR-BLOOD-DED-0330
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-BLOOD-DED-0330, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-BLOOD-DED-0330 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the float to integer group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Rounding boundary (x.499 / x.500) and integer storage; confirm the rounding rule (3 decimals vs whole number).
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="133" ht="156" customHeight="1">
       <c r="A133" s="5" t="n">
         <v>132</v>
       </c>
@@ -7745,8 +9393,18 @@
       <c r="K133" s="28" t="str">
         <v>Field MEDPAR-BLOOD-PINTS-0520: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="134" ht="48" customHeight="1">
+      <c r="L133" s="64" t="str">
+        <v>Item: 132 — MEDPAR-BLOOD-PINTS-0520
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-BLOOD-PINTS-0520, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-BLOOD-PINTS-0520 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="134" ht="156" customHeight="1">
       <c r="A134" s="5" t="n">
         <v>133</v>
       </c>
@@ -7794,8 +9452,18 @@
       <c r="K134" s="28" t="str">
         <v>Field MEDPAR-BNDLD-MOD-DSCT-PCT-0770: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="135" ht="36" customHeight="1">
+      <c r="L134" s="64" t="str">
+        <v>Item: 133 — MEDPAR-BNDLD-MOD-DSCT-PCT-0770
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-BNDLD-MOD-DSCT-PCT-0770, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-BNDLD-MOD-DSCT-PCT-0770 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move3 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="135" ht="156" customHeight="1">
       <c r="A135" s="5" t="n">
         <v>134</v>
       </c>
@@ -7843,8 +9511,18 @@
       <c r="K135" s="28" t="str">
         <v>Field MEDPAR-CAPITAL-ACC92-0382: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="136" ht="48" customHeight="1">
+      <c r="L135" s="64" t="str">
+        <v>Item: 134 — MEDPAR-CAPITAL-ACC92-0382
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-CAPITAL-ACC92-0382, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CAPITAL-ACC92-0382 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the float to integer group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Rounding boundary (x.499 / x.500) and integer storage; confirm the rounding rule (3 decimals vs whole number).
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="136" ht="156" customHeight="1">
       <c r="A136" s="5" t="n">
         <v>135</v>
       </c>
@@ -7892,8 +9570,18 @@
       <c r="K136" s="28" t="str">
         <v>Field MEDPAR-CAR-IMPRV-MOD-1-CD-0710: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="137" ht="48" customHeight="1">
+      <c r="L136" s="64" t="str">
+        <v>Item: 135 — MEDPAR-CAR-IMPRV-MOD-1-CD-0710
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-CAR-IMPRV-MOD-1-CD-0710, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CAR-IMPRV-MOD-1-CD-0710 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move3 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="137" ht="156" customHeight="1">
       <c r="A137" s="5" t="n">
         <v>136</v>
       </c>
@@ -7941,8 +9629,18 @@
       <c r="K137" s="28" t="str">
         <v>Field MEDPAR-CAR-IMPRV-MOD-2-CD-0720: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="138" ht="48" customHeight="1">
+      <c r="L137" s="64" t="str">
+        <v>Item: 136 — MEDPAR-CAR-IMPRV-MOD-2-CD-0720
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-CAR-IMPRV-MOD-2-CD-0720, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CAR-IMPRV-MOD-2-CD-0720 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move3 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="138" ht="156" customHeight="1">
       <c r="A138" s="5" t="n">
         <v>137</v>
       </c>
@@ -7990,8 +9688,18 @@
       <c r="K138" s="28" t="str">
         <v>Field MEDPAR-CAR-IMPRV-MOD-3-CD-0730: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="139" ht="48" customHeight="1">
+      <c r="L138" s="64" t="str">
+        <v>Item: 137 — MEDPAR-CAR-IMPRV-MOD-3-CD-0730
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-CAR-IMPRV-MOD-3-CD-0730, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CAR-IMPRV-MOD-3-CD-0730 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move3 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="139" ht="156" customHeight="1">
       <c r="A139" s="5" t="n">
         <v>138</v>
       </c>
@@ -8039,8 +9747,18 @@
       <c r="K139" s="28" t="str">
         <v>Field MEDPAR-CAR-IMPRV-MOD-4-CD-0740: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="140" ht="36" customHeight="1">
+      <c r="L139" s="64" t="str">
+        <v>Item: 138 — MEDPAR-CAR-IMPRV-MOD-4-CD-0740
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-CAR-IMPRV-MOD-4-CD-0740, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CAR-IMPRV-MOD-4-CD-0740 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move3 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="140" ht="156" customHeight="1">
       <c r="A140" s="5" t="n">
         <v>139</v>
       </c>
@@ -8088,8 +9806,18 @@
       <c r="K140" s="28" t="str">
         <v>Field MEDPAR-CLM-BENE-ID-TYP-CD-1430: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="141" ht="36" customHeight="1">
+      <c r="L140" s="64" t="str">
+        <v>Item: 139 — MEDPAR-CLM-BENE-ID-TYP-CD-1430
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-CLM-BENE-ID-TYP-CD-1430, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CLM-BENE-ID-TYP-CD-1430 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="141" ht="156" customHeight="1">
       <c r="A141" s="5" t="n">
         <v>140</v>
       </c>
@@ -8137,8 +9865,18 @@
       <c r="K141" s="28" t="str">
         <v>Field MEDPAR-CLM-DRG-GRPR-VRSN-1610: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="142" ht="48" customHeight="1">
+      <c r="L141" s="64" t="str">
+        <v>Item: 140 — MEDPAR-CLM-DRG-GRPR-VRSN-1610
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-CLM-DRG-GRPR-VRSN-1610, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CLM-DRG-GRPR-VRSN-1610 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="142" ht="156" customHeight="1">
       <c r="A142" s="5" t="n">
         <v>141</v>
       </c>
@@ -8186,8 +9924,18 @@
       <c r="K142" s="28" t="str">
         <v>Field MEDPAR-CLM-PNT-RLTNSHP-CD-0700: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="143" ht="36" customHeight="1">
+      <c r="L142" s="64" t="str">
+        <v>Item: 141 — MEDPAR-CLM-PNT-RLTNSHP-CD-0700
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-CLM-PNT-RLTNSHP-CD-0700, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CLM-PNT-RLTNSHP-CD-0700 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move3 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="143" ht="156" customHeight="1">
       <c r="A143" s="5" t="n">
         <v>142</v>
       </c>
@@ -8235,8 +9983,18 @@
       <c r="K143" s="28" t="str">
         <v>Field MEDPAR-CLM-PRCR-VRSN-1600: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="144" ht="36" customHeight="1">
+      <c r="L143" s="64" t="str">
+        <v>Item: 142 — MEDPAR-CLM-PRCR-VRSN-1600
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-CLM-PRCR-VRSN-1600, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CLM-PRCR-VRSN-1600 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="144" ht="156" customHeight="1">
       <c r="A144" s="5" t="n">
         <v>143</v>
       </c>
@@ -8284,8 +10042,18 @@
       <c r="K144" s="28" t="str">
         <v>Field MEDPAR-CLM-RP-IND-CD-1390: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="145" ht="36" customHeight="1">
+      <c r="L144" s="64" t="str">
+        <v>Item: 143 — MEDPAR-CLM-RP-IND-CD-1390
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-CLM-RP-IND-CD-1390, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-CLM-RP-IND-CD-1390 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="145" ht="156" customHeight="1">
       <c r="A145" s="5" t="n">
         <v>144</v>
       </c>
@@ -8333,8 +10101,18 @@
       <c r="K145" s="28" t="str">
         <v>Field MEDPAR-COIN-AMT-0310: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="146" ht="36" customHeight="1">
+      <c r="L145" s="64" t="str">
+        <v>Item: 144 — MEDPAR-COIN-AMT-0310
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-COIN-AMT-0310, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-COIN-AMT-0310 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the float to integer group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Rounding boundary (x.499 / x.500) and integer storage; confirm the rounding rule (3 decimals vs whole number).
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="146" ht="156" customHeight="1">
       <c r="A146" s="5" t="n">
         <v>145</v>
       </c>
@@ -8382,8 +10160,18 @@
       <c r="K146" s="28" t="str">
         <v>Field MEDPAR-COIN-DAYS-0290: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="147" ht="36" customHeight="1">
+      <c r="L146" s="64" t="str">
+        <v>Item: 145 — MEDPAR-COIN-DAYS-0290
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-COIN-DAYS-0290, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-COIN-DAYS-0290 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="147" ht="156" customHeight="1">
       <c r="A147" s="5" t="n">
         <v>146</v>
       </c>
@@ -8431,8 +10219,18 @@
       <c r="K147" s="28" t="str">
         <v>Field MEDPAR-COV-DAYS-0280: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="148" ht="24" customHeight="1">
+      <c r="L147" s="64" t="str">
+        <v>Item: 146 — MEDPAR-COV-DAYS-0280
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-COV-DAYS-0280, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-COV-DAYS-0280 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="148" ht="15" customHeight="1">
       <c r="A148" s="5" t="n">
         <v>147</v>
       </c>
@@ -8480,8 +10278,11 @@
       <c r="K148" s="28" t="str">
         <v>Field MEDPAR-DATE-OF-DATA-0620: Blank/filler deletion check. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. </v>
       </c>
-    </row>
-    <row r="149" ht="36" customHeight="1">
+      <c r="L148" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Excluded by the documented scope/deletion decision; no implementation is required unless scope changes.</v>
+      </c>
+    </row>
+    <row r="149" ht="156" customHeight="1">
       <c r="A149" s="5" t="n">
         <v>148</v>
       </c>
@@ -8529,8 +10330,18 @@
       <c r="K149" s="28" t="str">
         <v>Field MEDPAR-DISCHG-STATUS-0100: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="150" ht="36" customHeight="1">
+      <c r="L149" s="64" t="str">
+        <v>Item: 148 — MEDPAR-DISCHG-STATUS-0100
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-DISCHG-STATUS-0100, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-DISCHG-STATUS-0100 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="150" ht="156" customHeight="1">
       <c r="A150" s="5" t="n">
         <v>149</v>
       </c>
@@ -8578,8 +10389,18 @@
       <c r="K150" s="28" t="str">
         <v>Field MEDPAR-DRG-PRICE-0380: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="151" ht="36" customHeight="1">
+      <c r="L150" s="64" t="str">
+        <v>Item: 149 — MEDPAR-DRG-PRICE-0380
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-DRG-PRICE-0380, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-DRG-PRICE-0380 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="151" ht="156" customHeight="1">
       <c r="A151" s="5" t="n">
         <v>150</v>
       </c>
@@ -8627,8 +10448,18 @@
       <c r="K151" s="28" t="str">
         <v>Field MEDPAR-EHR-PGM-RDCTN-IND-1250: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="152" ht="36" customHeight="1">
+      <c r="L151" s="64" t="str">
+        <v>Item: 150 — MEDPAR-EHR-PGM-RDCTN-IND-1250
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-EHR-PGM-RDCTN-IND-1250, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-EHR-PGM-RDCTN-IND-1250 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="152" ht="156" customHeight="1">
       <c r="A152" s="5" t="n">
         <v>151</v>
       </c>
@@ -8676,8 +10507,18 @@
       <c r="K152" s="28" t="str">
         <v>Field MEDPAR-HAC-PGM-RDCTN-IND-1240: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="153" ht="36" customHeight="1">
+      <c r="L152" s="64" t="str">
+        <v>Item: 151 — MEDPAR-HAC-PGM-RDCTN-IND-1240
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-HAC-PGM-RDCTN-IND-1240, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-HAC-PGM-RDCTN-IND-1240 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="153" ht="156" customHeight="1">
       <c r="A153" s="5" t="n">
         <v>152</v>
       </c>
@@ -8725,8 +10566,18 @@
       <c r="K153" s="28" t="str">
         <v>Field MEDPAR-HMO-READM-0110: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="154" ht="36" customHeight="1">
+      <c r="L153" s="64" t="str">
+        <v>Item: 152 — MEDPAR-HMO-READM-0110
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-HMO-READM-0110, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-HMO-READM-0110 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="154" ht="156" customHeight="1">
       <c r="A154" s="5" t="n">
         <v>153</v>
       </c>
@@ -8774,8 +10625,18 @@
       <c r="K154" s="28" t="str">
         <v>Field MEDPAR-HRR-ADJSTMT-PCT-0790: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="155" ht="48" customHeight="1">
+      <c r="L154" s="64" t="str">
+        <v>Item: 153 — MEDPAR-HRR-ADJSTMT-PCT-0790
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-HRR-ADJSTMT-PCT-0790, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-HRR-ADJSTMT-PCT-0790 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move3 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="155" ht="156" customHeight="1">
       <c r="A155" s="5" t="n">
         <v>154</v>
       </c>
@@ -8823,8 +10684,18 @@
       <c r="K155" s="28" t="str">
         <v>Field MEDPAR-HRR-PRTCPNT-IND-CD-0760: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="156" ht="24" customHeight="1">
+      <c r="L155" s="64" t="str">
+        <v>Item: 154 — MEDPAR-HRR-PRTCPNT-IND-CD-0760
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-HRR-PRTCPNT-IND-CD-0760, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-HRR-PRTCPNT-IND-CD-0760 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move3 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="156" ht="15" customHeight="1">
       <c r="A156" s="5" t="n">
         <v>155</v>
       </c>
@@ -8872,8 +10743,11 @@
       <c r="K156" s="28" t="str">
         <v>Field MEDPAR-IMCAB-INFO-0619: Blank/filler deletion check. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. </v>
       </c>
-    </row>
-    <row r="157" ht="36" customHeight="1">
+      <c r="L156" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Excluded by the documented scope/deletion decision; no implementation is required unless scope changes.</v>
+      </c>
+    </row>
+    <row r="157" ht="156" customHeight="1">
       <c r="A157" s="5" t="n">
         <v>156</v>
       </c>
@@ -8921,8 +10795,18 @@
       <c r="K157" s="28" t="str">
         <v>Field MEDPAR-INPAT-DED-0320: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="158" ht="36" customHeight="1">
+      <c r="L157" s="64" t="str">
+        <v>Item: 156 — MEDPAR-INPAT-DED-0320
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-INPAT-DED-0320, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-INPAT-DED-0320 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the float to integer group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Rounding boundary (x.499 / x.500) and integer storage; confirm the rounding rule (3 decimals vs whole number).
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="158" ht="156" customHeight="1">
       <c r="A158" s="5" t="n">
         <v>157</v>
       </c>
@@ -8970,8 +10854,18 @@
       <c r="K158" s="28" t="str">
         <v>Field MEDPAR-INTMD-NUM-0580: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="159" ht="36" customHeight="1">
+      <c r="L158" s="64" t="str">
+        <v>Item: 157 — MEDPAR-INTMD-NUM-0580
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-INTMD-NUM-0580, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-INTMD-NUM-0580 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="159" ht="156" customHeight="1">
       <c r="A159" s="5" t="n">
         <v>158</v>
       </c>
@@ -9019,8 +10913,18 @@
       <c r="K159" s="28" t="str">
         <v>Field MEDPAR-IP-INITL-MS-DRG-CD-1460: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="160" ht="36" customHeight="1">
+      <c r="L159" s="64" t="str">
+        <v>Item: 158 — MEDPAR-IP-INITL-MS-DRG-CD-1460
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-IP-INITL-MS-DRG-CD-1460, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-IP-INITL-MS-DRG-CD-1460 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="160" ht="156" customHeight="1">
       <c r="A160" s="5" t="n">
         <v>159</v>
       </c>
@@ -9068,8 +10972,18 @@
       <c r="K160" s="28" t="str">
         <v>Field MEDPAR-IP-LOW-VOL-PMT-AMT-0386: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="161" ht="36" customHeight="1">
+      <c r="L160" s="64" t="str">
+        <v>Item: 159 — MEDPAR-IP-LOW-VOL-PMT-AMT-0386
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-IP-LOW-VOL-PMT-AMT-0386, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-IP-LOW-VOL-PMT-AMT-0386 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the float to integer group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Rounding boundary (x.499 / x.500) and integer storage; confirm the rounding rule (3 decimals vs whole number).
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="161" ht="156" customHeight="1">
       <c r="A161" s="5" t="n">
         <v>160</v>
       </c>
@@ -9117,8 +11031,18 @@
       <c r="K161" s="28" t="str">
         <v>Field MEDPAR-LIFE-RES-0300: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="162" ht="36" customHeight="1">
+      <c r="L161" s="64" t="str">
+        <v>Item: 160 — MEDPAR-LIFE-RES-0300
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-LIFE-RES-0300, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-LIFE-RES-0300 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="162" ht="156" customHeight="1">
       <c r="A162" s="5" t="n">
         <v>161</v>
       </c>
@@ -9166,8 +11090,18 @@
       <c r="K162" s="28" t="str">
         <v>Field MEDPAR-MBI-ID-1420: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="163" ht="36" customHeight="1">
+      <c r="L162" s="64" t="str">
+        <v>Item: 161 — MEDPAR-MBI-ID-1420
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-MBI-ID-1420, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-MBI-ID-1420 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="163" ht="156" customHeight="1">
       <c r="A163" s="5" t="n">
         <v>162</v>
       </c>
@@ -9215,8 +11149,18 @@
       <c r="K163" s="28" t="str">
         <v>Field MEDPAR-MRN-0670: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="164" ht="36" customHeight="1">
+      <c r="L163" s="64" t="str">
+        <v>Item: 162 — MEDPAR-MRN-0670
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-MRN-0670, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-MRN-0670 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="164" ht="156" customHeight="1">
       <c r="A164" s="5" t="n">
         <v>163</v>
       </c>
@@ -9264,8 +11208,18 @@
       <c r="K164" s="28" t="str">
         <v>Field MEDPAR-MSCODE-0060: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="165" ht="36" customHeight="1">
+      <c r="L164" s="64" t="str">
+        <v>Item: 163 — MEDPAR-MSCODE-0060
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-MSCODE-0060, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-MSCODE-0060 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="165" ht="156" customHeight="1">
       <c r="A165" s="5" t="n">
         <v>164</v>
       </c>
@@ -9313,8 +11267,18 @@
       <c r="K165" s="28" t="str">
         <v>Field MEDPAR-NCH-CLM-TYPE-CD: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="166" ht="36" customHeight="1">
+      <c r="L165" s="64" t="str">
+        <v>Item: 164 — MEDPAR-NCH-CLM-TYPE-CD
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-NCH-CLM-TYPE-CD, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-NCH-CLM-TYPE-CD (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="166" ht="156" customHeight="1">
       <c r="A166" s="5" t="n">
         <v>165</v>
       </c>
@@ -9362,8 +11326,18 @@
       <c r="K166" s="28" t="str">
         <v>Field MEDPAR-NG-ACO-IND-1-CD-1330: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="167" ht="36" customHeight="1">
+      <c r="L166" s="64" t="str">
+        <v>Item: 165 — MEDPAR-NG-ACO-IND-1-CD-1330
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-NG-ACO-IND-1-CD-1330, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-NG-ACO-IND-1-CD-1330 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="167" ht="156" customHeight="1">
       <c r="A167" s="5" t="n">
         <v>166</v>
       </c>
@@ -9411,8 +11385,18 @@
       <c r="K167" s="28" t="str">
         <v>Field MEDPAR-NG-ACO-IND-2-CD-1340: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="168" ht="36" customHeight="1">
+      <c r="L167" s="64" t="str">
+        <v>Item: 166 — MEDPAR-NG-ACO-IND-2-CD-1340
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-NG-ACO-IND-2-CD-1340, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-NG-ACO-IND-2-CD-1340 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="168" ht="156" customHeight="1">
       <c r="A168" s="5" t="n">
         <v>167</v>
       </c>
@@ -9460,8 +11444,18 @@
       <c r="K168" s="28" t="str">
         <v>Field MEDPAR-NG-ACO-IND-3-CD-1350: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="169" ht="36" customHeight="1">
+      <c r="L168" s="64" t="str">
+        <v>Item: 167 — MEDPAR-NG-ACO-IND-3-CD-1350
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-NG-ACO-IND-3-CD-1350, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-NG-ACO-IND-3-CD-1350 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="169" ht="156" customHeight="1">
       <c r="A169" s="5" t="n">
         <v>168</v>
       </c>
@@ -9509,8 +11503,18 @@
       <c r="K169" s="28" t="str">
         <v>Field MEDPAR-NG-ACO-IND-4-CD-1360: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="170" ht="36" customHeight="1">
+      <c r="L169" s="64" t="str">
+        <v>Item: 168 — MEDPAR-NG-ACO-IND-4-CD-1360
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-NG-ACO-IND-4-CD-1360, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-NG-ACO-IND-4-CD-1360 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="170" ht="156" customHeight="1">
       <c r="A170" s="5" t="n">
         <v>169</v>
       </c>
@@ -9558,8 +11562,18 @@
       <c r="K170" s="28" t="str">
         <v>Field MEDPAR-NG-ACO-IND-5-CD-1370: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="171" ht="36" customHeight="1">
+      <c r="L170" s="64" t="str">
+        <v>Item: 169 — MEDPAR-NG-ACO-IND-5-CD-1370
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-NG-ACO-IND-5-CD-1370, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-NG-ACO-IND-5-CD-1370 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="171" ht="156" customHeight="1">
       <c r="A171" s="5" t="n">
         <v>170</v>
       </c>
@@ -9607,8 +11621,18 @@
       <c r="K171" s="28" t="str">
         <v>Field MEDPAR-NO-OF-BILLS-0150: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="172" ht="36" customHeight="1">
+      <c r="L171" s="64" t="str">
+        <v>Item: 170 — MEDPAR-NO-OF-BILLS-0150
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-NO-OF-BILLS-0150, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-NO-OF-BILLS-0150 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="172" ht="156" customHeight="1">
       <c r="A172" s="5" t="n">
         <v>171</v>
       </c>
@@ -9656,8 +11680,18 @@
       <c r="K172" s="28" t="str">
         <v>Field MEDPAR-OP-PHYS-0660: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="173" ht="36" customHeight="1">
+      <c r="L172" s="64" t="str">
+        <v>Item: 171 — MEDPAR-OP-PHYS-0660
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-OP-PHYS-0660, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-OP-PHYS-0660 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="173" ht="156" customHeight="1">
       <c r="A173" s="5" t="n">
         <v>172</v>
       </c>
@@ -9705,8 +11739,18 @@
       <c r="K173" s="28" t="str">
         <v>Field MEDPAR-ORG-NPI-NUM: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="174" ht="36" customHeight="1">
+      <c r="L173" s="64" t="str">
+        <v>Item: 172 — MEDPAR-ORG-NPI-NUM
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-ORG-NPI-NUM, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ORG-NPI-NUM (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="174" ht="156" customHeight="1">
       <c r="A174" s="5" t="n">
         <v>173</v>
       </c>
@@ -9754,8 +11798,18 @@
       <c r="K174" s="28" t="str">
         <v>Field MEDPAR-OUTLIER-AMOUNT-0350: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="175" ht="36" customHeight="1">
+      <c r="L174" s="64" t="str">
+        <v>Item: 173 — MEDPAR-OUTLIER-AMOUNT-0350
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-OUTLIER-AMOUNT-0350, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-OUTLIER-AMOUNT-0350 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the float to integer group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Rounding boundary (x.499 / x.500) and integer storage; confirm the rounding rule (3 decimals vs whole number).
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="175" ht="156" customHeight="1">
       <c r="A175" s="5" t="n">
         <v>174</v>
       </c>
@@ -9803,8 +11857,18 @@
       <c r="K175" s="28" t="str">
         <v>Field MEDPAR-PRIMARY-AMOUNT-0340: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="176" ht="36" customHeight="1">
+      <c r="L175" s="64" t="str">
+        <v>Item: 174 — MEDPAR-PRIMARY-AMOUNT-0340
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-PRIMARY-AMOUNT-0340, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PRIMARY-AMOUNT-0340 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the float to integer group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Rounding boundary (x.499 / x.500) and integer storage; confirm the rounding rule (3 decimals vs whole number).
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="176" ht="156" customHeight="1">
       <c r="A176" s="5" t="n">
         <v>175</v>
       </c>
@@ -9852,8 +11916,18 @@
       <c r="K176" s="28" t="str">
         <v>Field MEDPAR-PRIMRY-PYR-0540: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="177" ht="48" customHeight="1">
+      <c r="L176" s="64" t="str">
+        <v>Item: 175 — MEDPAR-PRIMRY-PYR-0540
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-PRIMRY-PYR-0540, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PRIMRY-PYR-0540 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="177" ht="156" customHeight="1">
       <c r="A177" s="5" t="n">
         <v>176</v>
       </c>
@@ -9901,8 +11975,18 @@
       <c r="K177" s="28" t="str">
         <v>Field MEDPAR-PRIOR-AUTHRZTN-IND-1260: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="178" ht="36" customHeight="1">
+      <c r="L177" s="64" t="str">
+        <v>Item: 176 — MEDPAR-PRIOR-AUTHRZTN-IND-1260
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-PRIOR-AUTHRZTN-IND-1260, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PRIOR-AUTHRZTN-IND-1260 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="178" ht="156" customHeight="1">
       <c r="A178" s="5" t="n">
         <v>177</v>
       </c>
@@ -9950,8 +12034,18 @@
       <c r="K178" s="28" t="str">
         <v>Field MEDPAR-PRVDR-FULL-NUM-1660: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="179" ht="36" customHeight="1">
+      <c r="L178" s="64" t="str">
+        <v>Item: 177 — MEDPAR-PRVDR-FULL-NUM-1660
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-PRVDR-FULL-NUM-1660, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-PRVDR-FULL-NUM-1660 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="179" ht="156" customHeight="1">
       <c r="A179" s="5" t="n">
         <v>178</v>
       </c>
@@ -9999,8 +12093,18 @@
       <c r="K179" s="28" t="str">
         <v>Field MEDPAR-RACE-0050: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="180" ht="36" customHeight="1">
+      <c r="L179" s="64" t="str">
+        <v>Item: 178 — MEDPAR-RACE-0050
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-RACE-0050, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-RACE-0050 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="180" ht="156" customHeight="1">
       <c r="A180" s="5" t="n">
         <v>179</v>
       </c>
@@ -10048,8 +12152,18 @@
       <c r="K180" s="28" t="str">
         <v>Field MEDPAR-RSDL-PMT-IND-CD-1380: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="181" ht="24" customHeight="1">
+      <c r="L180" s="64" t="str">
+        <v>Item: 179 — MEDPAR-RSDL-PMT-IND-CD-1380
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-RSDL-PMT-IND-CD-1380, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-RSDL-PMT-IND-CD-1380 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="181" ht="15" customHeight="1">
       <c r="A181" s="5" t="n">
         <v>180</v>
       </c>
@@ -10097,8 +12211,11 @@
       <c r="K181" s="28" t="str">
         <v>Field MEDPAR-SAMPLE-SIZE-0630: Blank/filler deletion check. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. </v>
       </c>
-    </row>
-    <row r="182" ht="36" customHeight="1">
+      <c r="L181" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Excluded by the documented scope/deletion decision; no implementation is required unless scope changes.</v>
+      </c>
+    </row>
+    <row r="182" ht="156" customHeight="1">
       <c r="A182" s="5" t="n">
         <v>181</v>
       </c>
@@ -10146,8 +12263,18 @@
       <c r="K182" s="28" t="str">
         <v>Field MEDPAR-SEX-0040: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="183" ht="36" customHeight="1">
+      <c r="L182" s="64" t="str">
+        <v>Item: 181 — MEDPAR-SEX-0040
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-SEX-0040, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-SEX-0040 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="183" ht="156" customHeight="1">
       <c r="A183" s="5" t="n">
         <v>182</v>
       </c>
@@ -10195,8 +12322,18 @@
       <c r="K183" s="28" t="str">
         <v>Field MEDPAR-SSA-NO-0021: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="184" ht="36" customHeight="1">
+      <c r="L183" s="64" t="str">
+        <v>Item: 182 — MEDPAR-SSA-NO-0021
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-SSA-NO-0021, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-SSA-NO-0021 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="184" ht="156" customHeight="1">
       <c r="A184" s="5" t="n">
         <v>183</v>
       </c>
@@ -10244,8 +12381,18 @@
       <c r="K184" s="28" t="str">
         <v>Field MEDPAR-TOT-CHRG-0400: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="185" ht="36" customHeight="1">
+      <c r="L184" s="64" t="str">
+        <v>Item: 183 — MEDPAR-TOT-CHRG-0400
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-TOT-CHRG-0400, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-TOT-CHRG-0400 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the float to integer group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Rounding boundary (x.499 / x.500) and integer storage; confirm the rounding rule (3 decimals vs whole number).
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="185" ht="156" customHeight="1">
       <c r="A185" s="5" t="n">
         <v>184</v>
       </c>
@@ -10293,8 +12440,18 @@
       <c r="K185" s="28" t="str">
         <v>Field MEDPAR-TYPE-ADMIS-0570: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="186" ht="36" customHeight="1">
+      <c r="L185" s="64" t="str">
+        <v>Item: 184 — MEDPAR-TYPE-ADMIS-0570
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-TYPE-ADMIS-0570, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-TYPE-ADMIS-0570 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move2 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="186" ht="156" customHeight="1">
       <c r="A186" s="5" t="n">
         <v>185</v>
       </c>
@@ -10342,8 +12499,18 @@
       <c r="K186" s="28" t="str">
         <v>Field MEDPAR-UNIQ-TRKNG-NUM-1270: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="187" ht="36" customHeight="1">
+      <c r="L186" s="64" t="str">
+        <v>Item: 185 — MEDPAR-UNIQ-TRKNG-NUM-1270
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-UNIQ-TRKNG-NUM-1270, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-UNIQ-TRKNG-NUM-1270 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move4 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="187" ht="156" customHeight="1">
       <c r="A187" s="5" t="n">
         <v>186</v>
       </c>
@@ -10391,8 +12558,18 @@
       <c r="K187" s="28" t="str">
         <v>Field MEDPAR-VBP-ADJSTMT-PCT-0780: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="188" ht="48" customHeight="1">
+      <c r="L187" s="64" t="str">
+        <v>Item: 186 — MEDPAR-VBP-ADJSTMT-PCT-0780
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-VBP-ADJSTMT-PCT-0780, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-VBP-ADJSTMT-PCT-0780 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move3 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="188" ht="156" customHeight="1">
       <c r="A188" s="5" t="n">
         <v>187</v>
       </c>
@@ -10440,8 +12617,18 @@
       <c r="K188" s="28" t="str">
         <v>Field MEDPAR-VBP-PRTCPNT-IND-CD-0750: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="189" ht="24" customHeight="1">
+      <c r="L188" s="64" t="str">
+        <v>Item: 187 — MEDPAR-VBP-PRTCPNT-IND-CD-0750
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For MEDPAR-VBP-PRTCPNT-IND-CD-0750, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-VBP-PRTCPNT-IND-CD-0750 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move3 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="189" ht="15" customHeight="1">
       <c r="A189" s="5" t="n">
         <v>188</v>
       </c>
@@ -10489,8 +12676,11 @@
       <c r="K189" s="28" t="str">
         <v>Field MEDPAR-WARNING-IND-0640: Blank/filler deletion check. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. </v>
       </c>
-    </row>
-    <row r="190" ht="36" customHeight="1">
+      <c r="L189" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Excluded by the documented scope/deletion decision; no implementation is required unless scope changes.</v>
+      </c>
+    </row>
+    <row r="190" ht="156" customHeight="1">
       <c r="A190" s="5" t="n">
         <v>189</v>
       </c>
@@ -10538,8 +12728,18 @@
       <c r="K190" s="28" t="str">
         <v>Field MEDPAR-ZIP-0080: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="191" ht="36" customHeight="1">
+      <c r="L190" s="64" t="str">
+        <v>Item: 189 — MEDPAR-ZIP-0080
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For MEDPAR-ZIP-0080, a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for MEDPAR-ZIP-0080 (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Direct Move1 group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Source-to-target equality (source file vs actual_output); add the field to selected_fields.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="191" ht="156" customHeight="1">
       <c r="A191" s="5" t="n">
         <v>190</v>
       </c>
@@ -10587,8 +12787,18 @@
       <c r="K191" s="28" t="str">
         <v>Field Warning indicator 01 (adjustment): Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="192" ht="36" customHeight="1">
+      <c r="L191" s="64" t="str">
+        <v>Item: 190 — Warning indicator 01 (adjustment)
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For Warning indicator 01 (adjustment), a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for Warning indicator 01 (adjustment) (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Warning indicators group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive and negative case per code value; check the derived value, not only the golden value.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="192" ht="156" customHeight="1">
       <c r="A192" s="5" t="n">
         <v>191</v>
       </c>
@@ -10636,8 +12846,18 @@
       <c r="K192" s="28" t="str">
         <v>Field Warning indicator 06 (intermediary cancel): Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="193" ht="36" customHeight="1">
+      <c r="L192" s="64" t="str">
+        <v>Item: 191 — Warning indicator 06 (intermediary cancel)
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For Warning indicator 06 (intermediary cancel), a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for Warning indicator 06 (intermediary cancel) (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Warning indicators group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive and negative case per code value; check the derived value, not only the golden value.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="193" ht="156" customHeight="1">
       <c r="A193" s="5" t="n">
         <v>192</v>
       </c>
@@ -10685,8 +12905,18 @@
       <c r="K193" s="28" t="str">
         <v>Field Warning indicator 08 (duplicate / death&lt;admission): Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="194" ht="36" customHeight="1">
+      <c r="L193" s="64" t="str">
+        <v>Item: 192 — Warning indicator 08 (duplicate / death&lt;admission)
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For Warning indicator 08 (duplicate / death&lt;admission), a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for Warning indicator 08 (duplicate / death&lt;admission) (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Warning indicators group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive and negative case per code value; check the derived value, not only the golden value.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="194" ht="156" customHeight="1">
       <c r="A194" s="5" t="n">
         <v>193</v>
       </c>
@@ -10734,8 +12964,18 @@
       <c r="K194" s="28" t="str">
         <v>Field Warning indicator 02 (edit-code table error): Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="195" ht="36" customHeight="1">
+      <c r="L194" s="64" t="str">
+        <v>Item: 193 — Warning indicator 02 (edit-code table error)
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For Warning indicator 02 (edit-code table error), a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for Warning indicator 02 (edit-code table error) (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Warning indicators group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive and negative case per code value; check the derived value, not only the golden value.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="195" ht="156" customHeight="1">
       <c r="A195" s="5" t="n">
         <v>194</v>
       </c>
@@ -10783,8 +13023,18 @@
       <c r="K195" s="28" t="str">
         <v>Field Warning indicator 03 (payment/charge sign): Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="196" ht="48" customHeight="1">
+      <c r="L195" s="64" t="str">
+        <v>Item: 194 — Warning indicator 03 (payment/charge sign)
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For Warning indicator 03 (payment/charge sign), a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for Warning indicator 03 (payment/charge sign) (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Warning indicators group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive and negative case per code value; check the derived value, not only the golden value.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="196" ht="156" customHeight="1">
       <c r="A196" s="5" t="n">
         <v>195</v>
       </c>
@@ -10832,8 +13082,18 @@
       <c r="K196" s="28" t="str">
         <v>Field Warning indicator 04 (utilisation vs LOS days): Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="197" ht="36" customHeight="1">
+      <c r="L196" s="64" t="str">
+        <v>Item: 195 — Warning indicator 04 (utilisation vs LOS days)
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For Warning indicator 04 (utilisation vs LOS days), a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for Warning indicator 04 (utilisation vs LOS days) (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Warning indicators group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive and negative case per code value; check the derived value, not only the golden value.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="197" ht="156" customHeight="1">
       <c r="A197" s="5" t="n">
         <v>196</v>
       </c>
@@ -10881,8 +13141,18 @@
       <c r="K197" s="28" t="str">
         <v>Field Warning indicator 05 (single/multiple claim): Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="198" ht="36" customHeight="1">
+      <c r="L197" s="64" t="str">
+        <v>Item: 196 — Warning indicator 05 (single/multiple claim)
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For Warning indicator 05 (single/multiple claim), a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for Warning indicator 05 (single/multiple claim) (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Warning indicators group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive and negative case per code value; check the derived value, not only the golden value.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="198" ht="156" customHeight="1">
       <c r="A198" s="5" t="n">
         <v>197</v>
       </c>
@@ -10930,8 +13200,18 @@
       <c r="K198" s="28" t="str">
         <v>Field Warning indicator 07 (state/county valid): Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="199" ht="48" customHeight="1">
+      <c r="L198" s="64" t="str">
+        <v>Item: 197 — Warning indicator 07 (state/county valid)
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For Warning indicator 07 (state/county valid), a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for Warning indicator 07 (state/county valid) (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Warning indicators group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive and negative case per code value; check the derived value, not only the golden value.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="199" ht="156" customHeight="1">
       <c r="A199" s="5" t="n">
         <v>198</v>
       </c>
@@ -10979,8 +13259,18 @@
       <c r="K199" s="28" t="str">
         <v>Field Warning indicator 09 (pass-thru per diem): Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.</v>
       </c>
-    </row>
-    <row r="200" ht="36" customHeight="1">
+      <c r="L199" s="64" t="str">
+        <v>Item: 198 — Warning indicator 09 (pass-thru per diem)
+Completed: Independent source rule and full-register golden comparison. src/medpar_qa/stages/v3_fields.py; intermediate/business_rules.py
+Why still Partial: For Warning indicator 09 (pass-thru per diem), a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: CMS golden fixture and approved byte offset; see functionality rows for rule-specific limitations.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for Warning indicator 09 (pass-thru per diem) (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Warning indicators group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive and negative case per code value; check the derived value, not only the golden value.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Run the existing independent rule and golden comparison on matched approved production examples; validate the current byte representation, resolve differences and capture acceptance evidence. Existing unit tests do not replace this external acceptance.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="200" ht="156" customHeight="1">
       <c r="A200" s="5" t="n">
         <v>199</v>
       </c>
@@ -11028,8 +13318,18 @@
       <c r="K200" s="28" t="str">
         <v>Field Warning indicator 10 (RUGs stays): Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
-    </row>
-    <row r="201" ht="36" customHeight="1">
+      <c r="L200" s="64" t="str">
+        <v>Item: 199 — Warning indicator 10 (RUGs stays)
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For Warning indicator 10 (RUGs stays), a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for Warning indicator 10 (RUGs stays) (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Warning indicators group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive and negative case per code value; check the derived value, not only the golden value.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="201" ht="156" customHeight="1">
       <c r="A201" s="5" t="n">
         <v>200</v>
       </c>
@@ -11077,9 +13377,19 @@
       <c r="K201" s="28" t="str">
         <v>Field Warning indicators 11-17 (set to zero): Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py Evidence: Generic full-register comparison regression; no field-specific calculation certification.. Remaining acceptance/input: Approved source mapping/calculation and CMS golden fixture required.</v>
       </c>
+      <c r="L201" s="64" t="str">
+        <v>Item: 200 — Warning indicators 11-17 (set to zero)
+Completed: Canonical alias and full-register golden comparison added; independent derivation not established. src/medpar_qa/stages/v3_fields.py
+Why still Partial: For Warning indicators 11-17 (set to zero), a field name and a successful generic comparison do not prove the correct calculation or its position in the physical MEDPAR record. An independently approved expected value is needed to detect a consistently wrong source-to-output mapping.
+Missing: Approved source mapping/calculation and CMS golden fixture required.
+Requested evidence: Provide the current MPRRECL/UTLIPSNL entry for Warning indicators 11-17 (set to zero) (start byte, length, type, encoding/defaults), approved source-to-target mapping or calculation for the Warning indicators group, and matched source/expected MEDPAR records keyed to the same stay and processing cycle. Cover the original suggested regression cases: Positive and negative case per code value; check the derived value, not only the golden value.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Establish and implement an independent derivation from the approved mapping, test normal and edge cases, and compare with the approved golden output; validate the physical byte representation using the current copybook. Generic golden comparison alone is not calculation certification.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K201"/>
+  <autoFilter ref="A1:L201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11090,7 +13400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11106,6 +13416,7 @@
     <col width="22" customWidth="1" min="11" max="11"/>
     <col min="12" max="12" width="36" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="95" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="115" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -11170,8 +13481,11 @@
       <c r="M1" s="25" t="str">
         <v>Remarks by Srikanth</v>
       </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
+      <c r="N1" s="61" t="str">
+        <v>Reason and closure requirements by Srikanth</v>
+      </c>
+    </row>
+    <row r="2" ht="156" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>SRT-01</t>
@@ -11233,8 +13547,18 @@
       <c r="M2" s="28" t="str">
         <v>FA ordering includes descending query-code tie breaker; admission retained for Stay identity. src/medpar_qa/reference_data.py; src/medpar_qa/stages/common.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Actual sorted production baseline and EQ-BIC preparation still needed.</v>
       </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+      <c r="N2" s="64" t="str">
+        <v>Item: SRT-01 — Sort order of claims
+Completed: FA ordering includes descending query-code tie breaker; admission retained for Stay identity. src/medpar_qa/reference_data.py; src/medpar_qa/stages/common.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Actual sorted production baseline and EQ-BIC preparation still needed.
+Requested evidence: Provide the approved item described under Missing for SRT-01, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="3" ht="144" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>SRT-02</t>
@@ -11296,8 +13620,18 @@
       <c r="M3" s="28" t="str">
         <v>DOD JSON adapter excludes deaths through 1997 and validates duplicate matches. src/medpar_qa/reference_data.py; src/medpar_qa/stages/common.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: 29-to-30-byte feed layout and P suffix require approved feed specification.</v>
       </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+      <c r="N3" s="64" t="str">
+        <v>Item: SRT-02 — DOD file preparation: keep DOD &gt; 1997, append 'P' (29 -&gt; 30 bytes)
+Completed: DOD JSON adapter excludes deaths through 1997 and validates duplicate matches. src/medpar_qa/reference_data.py; src/medpar_qa/stages/common.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: 29-to-30-byte feed layout and P suffix require approved feed specification.
+Requested evidence: Provide the approved item described under Missing for SRT-02, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="4" ht="144" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>SRT-03</t>
@@ -11359,8 +13693,18 @@
       <c r="M4" s="28" t="str">
         <v>SSA/BIC identity aliases corrected; EQ-BIC service not invented. src/medpar_qa/reference_data.py; src/medpar_qa/stages/common.py Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: MPREQ030/UTLBICEQ equating tables/API and approved sex default.</v>
       </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
+      <c r="N4" s="64" t="str">
+        <v>Item: SRT-03 — EQ-BIC process (MPREQ030 / UTLBICEQ), sex assumed '1'
+Completed: SSA/BIC identity aliases corrected; EQ-BIC service not invented. src/medpar_qa/reference_data.py; src/medpar_qa/stages/common.py
+Why still Blocked: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: MPREQ030/UTLBICEQ equating tables/API and approved sex default.
+Requested evidence: Provide the approved item described under Missing for SRT-03, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="5" ht="144" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>SRT-04</t>
@@ -11422,8 +13766,18 @@
       <c r="M5" s="28" t="str">
         <v>Sample orchestration remains available. src/medpar_qa/reference_data.py; src/medpar_qa/stages/common.py Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Production history store and 600–700M-record execution environment.</v>
       </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+      <c r="N5" s="64" t="str">
+        <v>Item: SRT-04 — Sort/merge new quarter with 700M-record history
+Completed: Sample orchestration remains available. src/medpar_qa/reference_data.py; src/medpar_qa/stages/common.py
+Why still Blocked: The supplied small fixtures cannot demonstrate quarterly processing at 600–700 million records. Throughput and memory claims require a representative workload, production-like resources and an agreed service-level target.
+Missing: Production history store and 600–700M-record execution environment.
+Requested evidence: Provide a representative scale dataset or approved generator profile, target record/file volumes and distributions, production-like compute/storage configuration, and agreed elapsed-time/memory/restartability acceptance limits.
+Suggested responsible roles: Platform/performance team and business SLA owner.
+Closure criteria: Execute the scale run in that environment, retain volume/time/resource and recovery evidence, fix measured bottlenecks, and obtain acceptance against the agreed limits.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="6" ht="144" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>SRT-05</t>
@@ -11485,8 +13839,18 @@
       <c r="M6" s="28" t="str">
         <v>No unapproved legacy date-edit rules added. src/medpar_qa/reference_data.py; src/medpar_qa/stages/common.py Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Confirm whether MPRDATEVL/MPRDATEL is retained; notes permit removal.</v>
       </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+      <c r="N6" s="64" t="str">
+        <v>Item: SRT-05 — MPRDATEVL / MPRDATEL date-set edits (duplicate/missing dates, invalid cycle)
+Completed: No unapproved legacy date-edit rules added. src/medpar_qa/reference_data.py; src/medpar_qa/stages/common.py
+Why still Blocked: The remaining behavior is missing from, outdated in, or ambiguous between the supplied references. Only the owning business/legacy team can approve the authoritative decision table or current program mapping; choosing one interpretation silently could certify incorrect results.
+Missing: Confirm whether MPRDATEVL/MPRDATEL is retained; notes permit removal.
+Requested evidence: Provide the approved item described under Missing for SRT-05, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="7" ht="144" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>SRT-06</t>
@@ -11548,8 +13912,18 @@
       <c r="M7" s="28" t="str">
         <v>Physical input/output length contracts added. src/medpar_qa/reference_data.py; src/medpar_qa/stages/common.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Exact flag positions and initialisation from copybooks.</v>
       </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+      <c r="N7" s="64" t="str">
+        <v>Item: SRT-06 — 3 warning-flag bytes added to the front of each record
+Completed: Physical input/output length contracts added. src/medpar_qa/reference_data.py; src/medpar_qa/stages/common.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Exact flag positions and initialisation from copybooks.
+Requested evidence: Provide the approved item described under Missing for SRT-06, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>FA-01</t>
@@ -11611,6 +13985,9 @@
       <c r="M8" s="28" t="str">
         <v>Default FA bypass removed; covered-days &gt; LOS bypass applied at Final. src/medpar_qa/stages/final_action/ Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification remains external.</v>
       </c>
+      <c r="N8" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -11674,6 +14051,9 @@
       <c r="M9" s="28" t="str">
         <v>FA unsupported transaction/error audit path and reporting already present. src/medpar_qa/stages/final_action/ Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Production error fixtures.</v>
       </c>
+      <c r="N9" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -11737,6 +14117,9 @@
       <c r="M10" s="28" t="str">
         <v>Single-year continuation check already implemented. src/medpar_qa/stages/final_action/ Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: CMS golden verification.</v>
       </c>
+      <c r="N10" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -11800,8 +14183,11 @@
       <c r="M11" s="28" t="str">
         <v>900/875 group size limits already implemented. src/medpar_qa/stages/final_action/ Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Production boundary fixtures.</v>
       </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+      <c r="N11" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>FA-05</t>
@@ -11863,6 +14249,9 @@
       <c r="M12" s="28" t="str">
         <v>Rule 5 follows MM-FINAC-21/22: retain latest differing non-QC0 ICN; matching ICNs drop. src/medpar_qa/stages/final_action/ Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Older V3 p20 wording superseded by supplied requirements.</v>
       </c>
+      <c r="N12" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -11926,6 +14315,9 @@
       <c r="M13" s="28" t="str">
         <v>Rule 6 uses action code rather than transaction-code fallback. src/medpar_qa/stages/final_action/ Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: CMS golden verification.</v>
       </c>
+      <c r="N13" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -11989,8 +14381,11 @@
       <c r="M14" s="28" t="str">
         <v>QC2 rejected under supported QC0/1/3/5 policy. src/medpar_qa/stages/final_action/ Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Older July email describing QC&gt;0 includes QC2; newer clarification takes precedence.</v>
       </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
+      <c r="N14" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="15" ht="144" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>FA-08</t>
@@ -12052,8 +14447,18 @@
       <c r="M15" s="28" t="str">
         <v>Rules 7–10B covered; revised 10A handles QC0 dominance with latest non-QC0. src/medpar_qa/stages/final_action/ Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS authoritative ICN branch matrix and indistinguishable ordering ties.</v>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
+      <c r="N15" s="64" t="str">
+        <v>Item: FA-08 — Rules 7, 8, 9 wording: keep non-QC0 with non-matching control numbers
+Completed: Rules 7–10B covered; revised 10A handles QC0 dominance with latest non-QC0. src/medpar_qa/stages/final_action/
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: CMS authoritative ICN branch matrix and indistinguishable ordering ties.
+Requested evidence: Provide the approved item described under Missing for FA-08, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="16" ht="144" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>FA-09</t>
@@ -12115,6 +14520,16 @@
       <c r="M16" s="28" t="str">
         <v>IP/SNF class separation and audits present. src/medpar_qa/stages/final_action/ Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Full SNF-specific legacy edit logic.</v>
       </c>
+      <c r="N16" s="64" t="str">
+        <v>Item: FA-09 — Inpatient and SNF validated and netted separately
+Completed: IP/SNF class separation and audits present. src/medpar_qa/stages/final_action/
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Full SNF-specific legacy edit logic.
+Requested evidence: Provide the approved item described under Missing for FA-09, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -12178,8 +14593,11 @@
       <c r="M17" s="28" t="str">
         <v>FA record/group/IP/SNF statistics exported. src/medpar_qa/stages/final_action/ Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Compare production statistics to approved control totals.</v>
       </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
+      <c r="N17" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>FA-11</t>
@@ -12241,8 +14659,11 @@
       <c r="M18" s="28" t="str">
         <v>Outpatient rules 12–16 excluded by project scope. src/medpar_qa/stages/final_action/ Evidence: Existing regression suite; no production certification claimed.. </v>
       </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
+      <c r="N18" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Excluded by the documented scope/deletion decision; no implementation is required unless scope changes.</v>
+      </c>
+    </row>
+    <row r="19" ht="144" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>SPL-01</t>
@@ -12304,8 +14725,18 @@
       <c r="M19" s="28" t="str">
         <v>IP split indicator uses latest stay thru date and whole calendar window. src/medpar_qa/stages/split/processor.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Confirm max-thru versus canonical last-bill tie semantics against CMS baseline.</v>
       </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
+      <c r="N19" s="64" t="str">
+        <v>Item: SPL-01 — Which date picks the year box
+Completed: IP split indicator uses latest stay thru date and whole calendar window. src/medpar_qa/stages/split/processor.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Confirm max-thru versus canonical last-bill tie semantics against CMS baseline.
+Requested evidence: Provide the approved item described under Missing for SPL-01, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>SPL-02</t>
@@ -12367,8 +14798,11 @@
       <c r="M20" s="28" t="str">
         <v>SNF retained; indicator uses admission, zero admission falls back to from date. src/medpar_qa/stages/split/processor.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+      <c r="N20" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>SPL-03</t>
@@ -12430,8 +14864,11 @@
       <c r="M21" s="28" t="str">
         <v>Invalid transaction types enter exception audit and record accounting. src/medpar_qa/stages/split/processor.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: None for documented rule.</v>
       </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
+      <c r="N21" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>SPL-04</t>
@@ -12493,8 +14930,11 @@
       <c r="M22" s="28" t="str">
         <v>75-bill rejection removed per October clarification; all records retained. src/medpar_qa/stages/split/processor.py Evidence: Existing regression suite; no production certification claimed.. </v>
       </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
+      <c r="N22" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Excluded by the documented scope/deletion decision; no implementation is required unless scope changes.</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>SPL-05</t>
@@ -12556,8 +14996,11 @@
       <c r="M23" s="28" t="str">
         <v>Over-75 stays generate PASS audit without rejecting bills. src/medpar_qa/stages/split/processor.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: None for documented audit.</v>
       </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
+      <c r="N23" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="24" ht="144" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>SPL-06</t>
@@ -12619,8 +15062,18 @@
       <c r="M24" s="28" t="str">
         <v>Record and signed charge balances include retained, outside-window and exception records. src/medpar_qa/stages/split/processor.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Legacy per-file/weekly parameter control totals.</v>
       </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+      <c r="N24" s="64" t="str">
+        <v>Item: SPL-06 — Balancing report: input = output counts; low count per weekly process date
+Completed: Record and signed charge balances include retained, outside-window and exception records. src/medpar_qa/stages/split/processor.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Legacy per-file/weekly parameter control totals.
+Requested evidence: Provide the approved item described under Missing for SPL-06, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>SPL-07</t>
@@ -12682,8 +15135,11 @@
       <c r="M25" s="28" t="str">
         <v>Y0–Y3 mean years back from run year; suffix 0109/1012, no Q prefix. src/medpar_qa/stages/split/processor.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Run-year configuration must match production cycle.</v>
       </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
+      <c r="N25" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="26" ht="144" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>SPL-08</t>
@@ -12745,8 +15201,18 @@
       <c r="M26" s="28" t="str">
         <v>Synthetic demo exposes CAN-based 0.1% sample. src/medpar_qa/stages/split/processor.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Confirm optional sample-output scope; actual legacy sample feeds.</v>
       </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
+      <c r="N26" s="64" t="str">
+        <v>Item: SPL-08 — 0.1% / 1% sample file (last 3 of claim number = 595)
+Completed: Synthetic demo exposes CAN-based 0.1% sample. src/medpar_qa/stages/split/processor.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Confirm optional sample-output scope; actual legacy sample feeds.
+Requested evidence: Provide the approved item described under Missing for SPL-08, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>SPL-09</t>
@@ -12808,8 +15274,11 @@
       <c r="M27" s="28" t="str">
         <v>Split decisions, exceptions and statistics exported as stage audit JSON. src/medpar_qa/stages/split/processor.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: None for audit implementation.</v>
       </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
+      <c r="N27" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>STY-01</t>
@@ -12871,8 +15340,11 @@
       <c r="M28" s="28" t="str">
         <v>Stay key includes HICN, provider and admission; distinct admissions remain separate. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
+      <c r="N28" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="29" ht="144" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>STY-02</t>
@@ -12934,8 +15406,18 @@
       <c r="M29" s="28" t="str">
         <v>First/last/high/low/sum and first-nonblank rules added; LD-1314 research recovered from mail. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Conflicting low-volume-payment and procedure-date rules; full 54-field COBOL sum list.</v>
       </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
+      <c r="N29" s="64" t="str">
+        <v>Item: STY-02 — Field rules: first bill, last bill, first-last, high date, low date, stay-derived, sum total
+Completed: First/last/high/low/sum and first-nonblank rules added; LD-1314 research recovered from mail. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Conflicting low-volume-payment and procedure-date rules; full 54-field COBOL sum list.
+Requested evidence: Provide the approved item described under Missing for STY-02, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="30" ht="144" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>STY-03</t>
@@ -12997,8 +15479,18 @@
       <c r="M30" s="28" t="str">
         <v>Condition/occurrence/value/span consolidation and known caps checked. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Full 8-trailer layouts and approved modernized ordering; old research has index collisions.</v>
       </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
+      <c r="N30" s="64" t="str">
+        <v>Item: STY-03 — Trailer groups: NCH-EDIT, NCH-PATCH, MCO-PRD, CLM-PAYERID, CLM-DEMO-ID, CLM-DGNS, CLM-PRCDR, CLM-REV-CNTR
+Completed: Condition/occurrence/value/span consolidation and known caps checked. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Full 8-trailer layouts and approved modernized ordering; old research has index collisions.
+Requested evidence: Provide the approved item described under Missing for STY-03, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="31" ht="144" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>STY-04</t>
@@ -13060,8 +15552,18 @@
       <c r="M31" s="28" t="str">
         <v>Warning 01/05 calculations added. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Warnings 06/08 require authoritative net-action/cancel/duplicate policy.</v>
       </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
+      <c r="N31" s="64" t="str">
+        <v>Item: STY-04 — Warning indicators 01, 05, 06, 08 created in Stay
+Completed: Warning 01/05 calculations added. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Warnings 06/08 require authoritative net-action/cancel/duplicate policy.
+Requested evidence: Provide the approved item described under Missing for STY-04, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>STY-05</t>
@@ -13123,8 +15625,11 @@
       <c r="M32" s="28" t="str">
         <v>All revenue lines preserved; legacy 45-segment limit not imposed. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py Evidence: Existing regression suite; no production certification claimed.. </v>
       </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
+      <c r="N32" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Excluded by the documented scope/deletion decision; no implementation is required unless scope changes.</v>
+      </c>
+    </row>
+    <row r="33" ht="156" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>STY-06</t>
@@ -13186,8 +15691,18 @@
       <c r="M33" s="28" t="str">
         <v>Revenue-code structural range checks present; positive monetary cap now supplied by LD-1410. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Exact legacy accumulator widths and trailer limits.</v>
       </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
+      <c r="N33" s="64" t="str">
+        <v>Item: STY-06 — Revenue code validity 001-999; RUGs 9000-9044; overflow = all 9s
+Completed: Revenue-code structural range checks present; positive monetary cap now supplied by LD-1410. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Exact legacy accumulator widths and trailer limits.
+Requested evidence: Provide the approved item described under Missing for STY-06, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="34" ht="144" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>STY-07</t>
@@ -13249,8 +15764,18 @@
       <c r="M34" s="28" t="str">
         <v>Non-conflicting declared amount fields summed with Decimal precision. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Complete approved sum list; low-volume field conflicts first versus sum.</v>
       </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
+      <c r="N34" s="64" t="str">
+        <v>Item: STY-07 — 54 fields accumulated for multi-bill stays
+Completed: Non-conflicting declared amount fields summed with Decimal precision. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Complete approved sum list; low-volume field conflicts first versus sum.
+Requested evidence: Provide the approved item described under Missing for STY-07, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>STY-08</t>
@@ -13312,8 +15837,11 @@
       <c r="M35" s="28" t="str">
         <v>Diagnosis/procedure output checked from last bill per MM-Stay-15. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Old LD-1063 accumulation research conflicts; current requirement takes precedence.</v>
       </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
+      <c r="N35" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="36" ht="144" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>STY-09</t>
@@ -13375,8 +15903,18 @@
       <c r="M36" s="28" t="str">
         <v>Existing structural warning checks retained. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Approved warning 06/08 decision table and duplicate definition.</v>
       </c>
-    </row>
-    <row r="37" ht="36" customHeight="1">
+      <c r="N36" s="64" t="str">
+        <v>Item: STY-09 — Warning 6 and 8 rules
+Completed: Existing structural warning checks retained. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py
+Why still Blocked: The remaining behavior is missing from, outdated in, or ambiguous between the supplied references. Only the owning business/legacy team can approve the authoritative decision table or current program mapping; choosing one interpretation silently could certify incorrect results.
+Missing: Approved warning 06/08 decision table and duplicate definition.
+Requested evidence: Provide the approved item described under Missing for STY-09, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="37" ht="144" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>STY-10</t>
@@ -13438,8 +15976,18 @@
       <c r="M37" s="28" t="str">
         <v>32004→32007→32010 physical contracts verified when raw text is supplied. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Exact six-byte flag offsets and meaning.</v>
       </c>
-    </row>
-    <row r="38" ht="24" customHeight="1">
+      <c r="N37" s="64" t="str">
+        <v>Item: STY-10 — Header bytes on the stay record
+Completed: 32004→32007→32010 physical contracts verified when raw text is supplied. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Exact six-byte flag offsets and meaning.
+Requested evidence: Provide the approved item described under Missing for STY-10, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="38" ht="144" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>STY-11</t>
@@ -13501,8 +16049,18 @@
       <c r="M38" s="28" t="str">
         <v>Optional sample products not fabricated. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Confirm five sample outputs and their routing rules.</v>
       </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
+      <c r="N38" s="64" t="str">
+        <v>Item: STY-11 — 5 output files (5/15/20/60%)
+Completed: Optional sample products not fabricated. src/medpar_qa/stages/stay/merge_rules.py; code_precedence.py
+Why still Blocked: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Confirm five sample outputs and their routing rules.
+Requested evidence: Provide the approved item described under Missing for STY-11, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
           <t>INT-01</t>
@@ -13564,8 +16122,11 @@
       <c r="M39" s="28" t="str">
         <v>LOS derived independently, same-day minimum 1 and still-patient +1. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
+      <c r="N39" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="40" ht="144" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
           <t>INT-02</t>
@@ -13627,8 +16188,18 @@
       <c r="M40" s="28" t="str">
         <v>DOD lookup, &gt;1997 cutoff, death fallback to thru and verify B implemented. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: EQ-BIC/cache feed mapping and approved production DOD fixture.</v>
       </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
+      <c r="N40" s="64" t="str">
+        <v>Item: INT-02 — Date of death lookup and verify switch
+Completed: DOD lookup, &gt;1997 cutoff, death fallback to thru and verify B implemented. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: EQ-BIC/cache feed mapping and approved production DOD fixture.
+Requested evidence: Provide the approved item described under Missing for INT-02, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>INT-03</t>
@@ -13690,8 +16261,11 @@
       <c r="M41" s="28" t="str">
         <v>Death-after-admission is day count; same day 1, missing DOD blank. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="42" ht="48" customHeight="1">
+      <c r="N41" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="42" ht="144" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
           <t>INT-04</t>
@@ -13753,8 +16327,18 @@
       <c r="M42" s="28" t="str">
         <v>SSI monthly overlap uses admission inclusive/discharge exclusive and merged positive flags. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: 0253 secondary field and full approved cache/binary table representation.</v>
       </c>
-    </row>
-    <row r="43" ht="24" customHeight="1">
+      <c r="N42" s="64" t="str">
+        <v>Item: INT-04 — SSI days and indicator (0251-0253)
+Completed: SSI monthly overlap uses admission inclusive/discharge exclusive and merged positive flags. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: 0253 secondary field and full approved cache/binary table representation.
+Requested evidence: Provide the approved item described under Missing for INT-04, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="43" ht="144" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
           <t>INT-05</t>
@@ -13816,8 +16400,18 @@
       <c r="M43" s="28" t="str">
         <v>DRG golden field comparison included. src/medpar_qa/stages/intermediate/business_rules.py Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Licensed/versioned DRG grouper, outlier tables and approved expected results.</v>
       </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
+      <c r="N43" s="64" t="str">
+        <v>Item: INT-05 — DRG code and DRG module choice
+Completed: DRG golden field comparison included. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Blocked: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Licensed/versioned DRG grouper, outlier tables and approved expected results.
+Requested evidence: Provide the approved item described under Missing for INT-05, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
           <t>INT-06</t>
@@ -13879,8 +16473,11 @@
       <c r="M44" s="28" t="str">
         <v>DRG price recalculated from six raw amounts with whole-dollar rounding. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
+      <c r="N44" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
           <t>INT-07</t>
@@ -13942,8 +16539,11 @@
       <c r="M45" s="28" t="str">
         <v>PPS indicator checks numeric provider position and absent condition 65. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="46" ht="24" customHeight="1">
+      <c r="N45" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="46" ht="144" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
           <t>INT-08</t>
@@ -14005,8 +16605,18 @@
       <c r="M46" s="28" t="str">
         <v>Final class format S/L/N corrected. src/medpar_qa/stages/intermediate/business_rules.py Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Current COBOL special-unit/class derivation; V3 says rules outdated.</v>
       </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
+      <c r="N46" s="64" t="str">
+        <v>Item: INT-08 — Special unit code (0137) and SS/LS/SNF (0140)
+Completed: Final class format S/L/N corrected. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Blocked: The remaining behavior is missing from, outdated in, or ambiguous between the supplied references. Only the owning business/legacy team can approve the authoritative decision table or current program mapping; choosing one interpretation silently could certify incorrect results.
+Missing: Current COBOL special-unit/class derivation; V3 says rules outdated.
+Requested evidence: Provide the approved item described under Missing for INT-08, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t>INT-09</t>
@@ -14068,8 +16678,11 @@
       <c r="M47" s="28" t="str">
         <v>Documented base-facility CCN positional mapping implemented. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
+      <c r="N47" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
           <t>INT-10</t>
@@ -14131,8 +16744,11 @@
       <c r="M48" s="28" t="str">
         <v>Age at admission computed; age64/MS10 or11 becomes65. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="49" ht="36" customHeight="1">
+      <c r="N48" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
           <t>INT-11</t>
@@ -14194,8 +16810,11 @@
       <c r="M49" s="28" t="str">
         <v>Discharge A/B/C mapped from alive/dead/still-patient source status. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
+      <c r="N49" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
           <t>INT-12</t>
@@ -14257,8 +16876,11 @@
       <c r="M50" s="28" t="str">
         <v>Strict YYYYDDD/YYDDD parsing and Julian field conversions added. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
+      <c r="N50" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
           <t>INT-13</t>
@@ -14320,8 +16942,11 @@
       <c r="M51" s="28" t="str">
         <v>Benefits-exhausted date converts to Julian from provided source. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
+      <c r="N51" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="52" ht="144" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
           <t>INT-14</t>
@@ -14383,8 +17008,18 @@
       <c r="M52" s="28" t="str">
         <v>Span70/72/82/22 derivations added, highest SNF care end and midnight switch. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Approved HAH limits, source span ordering and reference windows.</v>
       </c>
-    </row>
-    <row r="53" ht="36" customHeight="1">
+      <c r="N52" s="64" t="str">
+        <v>Item: INT-14 — SNF qualification (span 70), 2-midnight (span 72), hospital-at-home (span 82), covered level care (span 22)
+Completed: Span70/72/82/22 derivations added, highest SNF care end and midnight switch. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Approved HAH limits, source span ordering and reference windows.
+Requested evidence: Provide the approved item described under Missing for INT-14, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
           <t>INT-15</t>
@@ -14446,8 +17081,11 @@
       <c r="M53" s="28" t="str">
         <v>ESRD condition uses highest code71–76. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="54" ht="36" customHeight="1">
+      <c r="N53" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
           <t>INT-16</t>
@@ -14509,6 +17147,9 @@
       <c r="M54" s="28" t="str">
         <v>Condition91 maps emergency switch Y. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
+      <c r="N54" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -14572,8 +17213,11 @@
       <c r="M55" s="28" t="str">
         <v>Highest valid organ revenue derives the documented type. 0818 is excluded and no-organ output is blank. Evidence: tests/unit/test_gap_register_business_rules.py. Remaining acceptance/input: CMS golden verification remains external.</v>
       </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
+      <c r="N55" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="56" ht="144" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
           <t>INT-18</t>
@@ -14635,8 +17279,18 @@
       <c r="M56" s="28" t="str">
         <v>Seven value amounts and FD switch derived;17 direct monetary moves covered; LD-1421 recovered. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Additional legacy mappings and approved production fixtures.</v>
       </c>
-    </row>
-    <row r="57" ht="36" customHeight="1">
+      <c r="N56" s="64" t="str">
+        <v>Item: INT-18 — Value codes: 18 -&gt; 0360, 19 -&gt; 0370, FD -&gt; 0840, 77 -&gt; 0860, Q7 -&gt; 1450, Q1 -&gt; 1470, QB -&gt; 1500, 73 -&gt; 1130
+Completed: Seven value amounts and FD switch derived;17 direct monetary moves covered; LD-1421 recovered. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Additional legacy mappings and approved production fixtures.
+Requested evidence: Provide the approved item described under Missing for INT-18, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
           <t>INT-19</t>
@@ -14698,8 +17352,11 @@
       <c r="M57" s="28" t="str">
         <v>Recovered LD-1410 COBOL: round rate to integer before days; cap positive total at999999999. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="58" ht="24" customHeight="1">
+      <c r="N57" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="58" ht="144" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
           <t>INT-20</t>
@@ -14761,8 +17418,18 @@
       <c r="M58" s="28" t="str">
         <v>All registered totals included in golden comparison. src/medpar_qa/stages/intermediate/business_rules.py Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Full 40+ revenue category mapping and approved legacy calculation baseline.</v>
       </c>
-    </row>
-    <row r="59" ht="24" customHeight="1">
+      <c r="N58" s="64" t="str">
+        <v>Item: INT-20 — Revenue-code group accumulation (28 groups) and revenue totals 0890-1120
+Completed: All registered totals included in golden comparison. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Blocked: The remaining behavior is missing from, outdated in, or ambiguous between the supplied references. Only the owning business/legacy team can approve the authoritative decision table or current program mapping; choosing one interpretation silently could certify incorrect results.
+Missing: Full 40+ revenue category mapping and approved legacy calculation baseline.
+Requested evidence: Provide the approved item described under Missing for INT-20, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="59" ht="156" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
           <t>INT-21</t>
@@ -14824,8 +17491,18 @@
       <c r="M59" s="28" t="str">
         <v>Radiology and outpatient types 0–3 are checked. ICU/CCU types use accumulated source charges with missing-charge/tie blocks. Evidence: tests/unit/test_gap_register_business_rules.py. Remaining acceptance/input: ESRD setting requires the approved current MPRPARL mapping.</v>
       </c>
-    </row>
-    <row r="60" ht="36" customHeight="1">
+      <c r="N59" s="64" t="str">
+        <v>Item: INT-21 — Radiology indicators, outpatient flag (490-509), ESRD setting codes
+Completed: Radiology and outpatient types0–3 checked;ICU/CCU types use accumulated charges with missing-charge/tie blocks. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: ESRD setting requires approved current MPRPARL mapping.
+Requested evidence: Provide the approved item described under Missing for INT-21, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
           <t>INT-22</t>
@@ -14887,8 +17564,11 @@
       <c r="M60" s="28" t="str">
         <v>Five accommodation groups derived including RUG revenue ranges and rounded group charges. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="61" ht="36" customHeight="1">
+      <c r="N60" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="61" ht="144" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
           <t>INT-23</t>
@@ -14950,8 +17630,18 @@
       <c r="M61" s="28" t="str">
         <v>Warning01/05 at Stay and04/09/11–17 at Intermediate implemented. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Full03/06/07/08/10 decision tables; warning10 duplicate wording unresolved.</v>
       </c>
-    </row>
-    <row r="62" ht="36" customHeight="1">
+      <c r="N61" s="64" t="str">
+        <v>Item: INT-23 — Warning indicators 02, 03, 04, 07, 09, 10; 11-17 = 0
+Completed: Warning01/05 at Stay and04/09/11–17 at Intermediate implemented. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Full03/06/07/08/10 decision tables; warning10 duplicate wording unresolved.
+Requested evidence: Provide the approved item described under Missing for INT-23, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
           <t>INT-24</t>
@@ -15013,8 +17703,11 @@
       <c r="M62" s="28" t="str">
         <v>Whole-dollar half-away-zero storage checks; positive9-digit cap from recovered LD-1410. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Negative field-width handling still depends on copybook.</v>
       </c>
-    </row>
-    <row r="63" ht="48" customHeight="1">
+      <c r="N62" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="63" ht="156" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
           <t>INT-25</t>
@@ -15076,8 +17769,18 @@
       <c r="M63" s="28" t="str">
         <v>Full200-field golden comparison; source-based LD-1407/1408 direct and ACO moves, MRN fallback, 5% sample added. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Remaining direct-move mappings and current-approved offsets; derived fields excluded from blind copying.</v>
       </c>
-    </row>
-    <row r="64" ht="36" customHeight="1">
+      <c r="N63" s="64" t="str">
+        <v>Item: INT-25 — Direct Move 1-4 fields (about 55)
+Completed: Full200-field golden comparison; source-based LD-1407/1408 direct and ACO moves, MRN fallback, 5% sample added. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Remaining direct-move mappings and current-approved offsets; derived fields excluded from blind copying.
+Requested evidence: Provide the approved item described under Missing for INT-25, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="64" ht="144" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
           <t>INT-26</t>
@@ -15139,8 +17842,18 @@
       <c r="M64" s="28" t="str">
         <v>3050-byte physical output check added. src/medpar_qa/stages/intermediate/business_rules.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: MPRRECL/UTLIPSNL offsets to rebuild exact fixed-width record from columns.</v>
       </c>
-    </row>
-    <row r="65" ht="24" customHeight="1">
+      <c r="N64" s="64" t="str">
+        <v>Item: INT-26 — 3,050-byte record: 3,000 + AT-PHYS, OP-PHYS, MRN, SAMPLE-05
+Completed: 3050-byte physical output check added. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: MPRRECL/UTLIPSNL offsets to rebuild exact fixed-width record from columns.
+Requested evidence: Provide the approved item described under Missing for INT-26, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
           <t>INT-27</t>
@@ -15202,8 +17915,11 @@
       <c r="M65" s="28" t="str">
         <v>Deleted outlier-days field treated as blank/filler. src/medpar_qa/stages/intermediate/business_rules.py Evidence: Existing regression suite; no production certification claimed.. </v>
       </c>
-    </row>
-    <row r="66" ht="36" customHeight="1">
+      <c r="N65" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Excluded by the documented scope/deletion decision; no implementation is required unless scope changes.</v>
+      </c>
+    </row>
+    <row r="66" ht="144" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
           <t>INT-28</t>
@@ -15265,8 +17981,18 @@
       <c r="M66" s="28" t="str">
         <v>Structural checks retained without inventing edit-table values. src/medpar_qa/stages/intermediate/business_rules.py Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Approved state/county/provider/revenue/discharge edit tables.</v>
       </c>
-    </row>
-    <row r="67" ht="36" customHeight="1">
+      <c r="N66" s="64" t="str">
+        <v>Item: INT-28 — Edit tables in code (provider numbers, state/county ranges, revenue categories, patient status)
+Completed: Structural checks retained without inventing edit-table values. src/medpar_qa/stages/intermediate/business_rules.py
+Why still Blocked: The remaining behavior is missing from, outdated in, or ambiguous between the supplied references. Only the owning business/legacy team can approve the authoritative decision table or current program mapping; choosing one interpretation silently could certify incorrect results.
+Missing: Approved state/county/provider/revenue/discharge edit tables.
+Requested evidence: Provide the approved item described under Missing for INT-28, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
           <t>FIN-01</t>
@@ -15328,8 +18054,11 @@
       <c r="M67" s="28" t="str">
         <v>Covered days &gt; LOS bypass handled before Final presence/golden checks and exported. src/medpar_qa/stages/final_medpar/business_rules.py; processor.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="68" ht="24" customHeight="1">
+      <c r="N67" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="68" ht="144" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
           <t>FIN-02</t>
@@ -15391,8 +18120,18 @@
       <c r="M68" s="28" t="str">
         <v>Stage audit and demo files available. src/medpar_qa/stages/final_medpar/business_rules.py; processor.py Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: 14-file CY/FY routing mapping and names from approved architecture.</v>
       </c>
-    </row>
-    <row r="69" ht="36" customHeight="1">
+      <c r="N68" s="64" t="str">
+        <v>Item: FIN-02 — Route to SS/LS or SNF files, by CY and FY (4 outputs; 6 inputs/outputs)
+Completed: Stage audit and demo files available. src/medpar_qa/stages/final_medpar/business_rules.py; processor.py
+Why still Blocked: Available q61 snapshots do not provide a complete, matched production chain through Final MEDPAR. A synthetic chain can test QA behavior but cannot establish production file routing, physical layout or final-output acceptance.
+Missing: 14-file CY/FY routing mapping and names from approved architecture.
+Requested evidence: Provide the approved item described under Missing for FIN-02, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="69" ht="24" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
           <t>FIN-03</t>
@@ -15454,8 +18193,11 @@
       <c r="M69" s="28" t="str">
         <v>Allowed classification corrected to one byte S/L/N. src/medpar_qa/stages/final_medpar/business_rules.py; processor.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Independent class derivation tracked in INT-08.</v>
       </c>
-    </row>
-    <row r="70" ht="36" customHeight="1">
+      <c r="N69" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="70" ht="24" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
           <t>FIN-04</t>
@@ -15517,8 +18259,11 @@
       <c r="M70" s="28" t="str">
         <v>3050→3000 compares exact first3000 bytes;50-byte trailing data removed. src/medpar_qa/stages/final_medpar/business_rules.py; processor.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Full serialization from columns tracked in WP-02.</v>
       </c>
-    </row>
-    <row r="71" ht="24" customHeight="1">
+      <c r="N70" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="71" ht="144" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
           <t>FIN-05</t>
@@ -15580,8 +18325,18 @@
       <c r="M71" s="28" t="str">
         <v>Distinct-admission stays preserved. src/medpar_qa/stages/final_medpar/business_rules.py; processor.py Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Approved HICN merge-equivalence rule; no collapse based only on HICN.</v>
       </c>
-    </row>
-    <row r="72" ht="36" customHeight="1">
+      <c r="N71" s="64" t="str">
+        <v>Item: FIN-05 — Merge on HIC number across inputs
+Completed: Distinct-admission stays preserved. src/medpar_qa/stages/final_medpar/business_rules.py; processor.py
+Why still Blocked: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Approved HICN merge-equivalence rule; no collapse based only on HICN.
+Requested evidence: Provide the approved item described under Missing for FIN-05, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="72" ht="144" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
           <t>FIN-06</t>
@@ -15643,8 +18398,18 @@
       <c r="M72" s="28" t="str">
         <v>Synthetic demo supports discharged IP and SNF stays. src/medpar_qa/stages/final_medpar/business_rules.py; processor.py Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: Resolve V3 look-into note for undischarged inclusion and production routing.</v>
       </c>
-    </row>
-    <row r="73" ht="36" customHeight="1">
+      <c r="N72" s="64" t="str">
+        <v>Item: FIN-06 — Inclusion rule: inpatient with discharge date; SNF even without
+Completed: Synthetic demo supports discharged IP and SNF stays. src/medpar_qa/stages/final_medpar/business_rules.py; processor.py
+Why still Partial: Available q61 snapshots do not provide a complete, matched production chain through Final MEDPAR. A synthetic chain can test QA behavior but cannot establish production file routing, physical layout or final-output acceptance.
+Missing: Resolve V3 look-into note for undischarged inclusion and production routing.
+Requested evidence: Provide the approved item described under Missing for FIN-06, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="73" ht="144" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
           <t>FIN-07</t>
@@ -15706,8 +18471,18 @@
       <c r="M73" s="28" t="str">
         <v>No undocumented BayState feed constructed. src/medpar_qa/stages/final_medpar/business_rules.py; processor.py Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Approved BayState input/output mapping and inclusion in submission.</v>
       </c>
-    </row>
-    <row r="74" ht="24" customHeight="1">
+      <c r="N73" s="64" t="str">
+        <v>Item: FIN-07 — Feed to BayState Quarterly
+Completed: No undocumented BayState feed constructed. src/medpar_qa/stages/final_medpar/business_rules.py; processor.py
+Why still Blocked: BayState inputs and approved output examples were not supplied. The framework cannot validate an unprovided feed or invent the two extra SSI fields and their physical layout.
+Missing: Approved BayState input/output mapping and inclusion in submission.
+Requested evidence: Provide the approved item described under Missing for FIN-07, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: BayState/DB2 feed owner and MedPAR business owner.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="74" ht="144" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
           <t>BAY-01</t>
@@ -15769,8 +18544,18 @@
       <c r="M74" s="28" t="str">
         <v>Scope and ambiguous DB2 derivation documented. No approved BayState adapter available Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: BayState scope, DB2 extract and corrected LOS/SSI formulas.</v>
       </c>
-    </row>
-    <row r="75" ht="24" customHeight="1">
+      <c r="N74" s="64" t="str">
+        <v>Item: BAY-01 — SSI recalculation on DB2 tables (MPRBCL21/22)
+Completed: Scope and ambiguous DB2 derivation documented. No approved BayState adapter available
+Why still Blocked: BayState inputs and approved output examples were not supplied. The framework cannot validate an unprovided feed or invent the two extra SSI fields and their physical layout.
+Missing: BayState scope, DB2 extract and corrected LOS/SSI formulas.
+Requested evidence: Provide the approved item described under Missing for BAY-01, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: BayState/DB2 feed owner and MedPAR business owner.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="75" ht="144" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
           <t>BAY-02</t>
@@ -15832,9 +18617,19 @@
       <c r="M75" s="28" t="str">
         <v>3004-byte BayState format not guessed. No approved BayState adapter available Evidence: Existing regression suite; no production certification claimed.. Remaining acceptance/input: Encoding/offsets for two additional fields and golden output.</v>
       </c>
+      <c r="N75" s="64" t="str">
+        <v>Item: BAY-02 — Output adds 2 fields: recalculated SSI day count (int) and indicator Y/N
+Completed: 3004-byte BayState format not guessed. No approved BayState adapter available
+Why still Blocked: BayState inputs and approved output examples were not supplied. The framework cannot validate an unprovided feed or invent the two extra SSI fields and their physical layout.
+Missing: Encoding/offsets for two additional fields and golden output.
+Requested evidence: Provide the approved item described under Missing for BAY-02, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: BayState/DB2 feed owner and MedPAR business owner.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M75"/>
+  <autoFilter ref="A1:N75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15845,7 +18640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15855,6 +18650,7 @@
     <col width="60" customWidth="1" min="5" max="5"/>
     <col min="6" max="6" width="36" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="95" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="115" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -15889,8 +18685,11 @@
       <c r="G1" s="25" t="str">
         <v>Remarks by Srikanth</v>
       </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
+      <c r="H1" s="61" t="str">
+        <v>Reason and closure requirements by Srikanth</v>
+      </c>
+    </row>
+    <row r="2" ht="144" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>WP-01</t>
@@ -15922,8 +18721,18 @@
       <c r="G2" s="28" t="str">
         <v>Five-stage synthetic chained demo and integration test available. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. Remaining acceptance/input: Full production chain still needs missing feed/layout/routing contracts.</v>
       </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
+      <c r="H2" s="64" t="str">
+        <v>Item: WP-01 — No end-to-end chain test
+Completed: Five-stage synthetic chained demo and integration test available.
+Why still Partial: Available q61 snapshots do not provide a complete, matched production chain through Final MEDPAR. A synthetic chain can test QA behavior but cannot establish production file routing, physical layout or final-output acceptance.
+Missing: Full production chain still needs missing feed/layout/routing contracts.
+Requested evidence: Provide the approved item described under Missing for WP-01, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="3" ht="144" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>WP-02</t>
@@ -15955,6 +18764,16 @@
       <c r="G3" s="28" t="str">
         <v>All stage raw lengths and exact Final prefix checked. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. Remaining acceptance/input: Approved copybooks required for reconstruction.</v>
       </c>
+      <c r="H3" s="64" t="str">
+        <v>Item: WP-02 — Record-length contract (32,004 / 32,007 / 32,010 / 3,050 / 3,000)
+Completed: All stage raw lengths and exact Final prefix checked.
+Why still Partial: Available q61 snapshots do not provide a complete, matched production chain through Final MEDPAR. A synthetic chain can test QA behavior but cannot establish production file routing, physical layout or final-output acceptance.
+Missing: Approved copybooks required for reconstruction.
+Requested evidence: Provide the approved item described under Missing for WP-02, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -15988,6 +18807,9 @@
       <c r="G4" s="28" t="str">
         <v>All200 Field Register rows included in golden comparison. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. Remaining acceptance/input: Supply golden values; absent on both sides explicitly N/A.</v>
       </c>
+      <c r="H4" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -16021,6 +18843,9 @@
       <c r="G5" s="28" t="str">
         <v>Case/separator-insensitive resolver and lower-case Parquet regression. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. Remaining acceptance/input: Production export smoke test.</v>
       </c>
+      <c r="H5" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -16054,8 +18879,11 @@
       <c r="G6" s="28" t="str">
         <v>Nested list/struct Parquet regression. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. Remaining acceptance/input: Production export smoke test.</v>
       </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
+      <c r="H6" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="7" ht="144" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>WP-06</t>
@@ -16087,6 +18915,16 @@
       <c r="G7" s="28" t="str">
         <v>DOD/SSI fixture feeds and fail-closed reference adapters. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. Remaining acceptance/input: DRG/outlier/IDR feeds and EQ-BIC contract.</v>
       </c>
+      <c r="H7" s="64" t="str">
+        <v>Item: WP-06 — External feeds are not modelled
+Completed: DOD/SSI fixture feeds and fail-closed reference adapters.
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: DRG/outlier/IDR feeds and EQ-BIC contract.
+Requested evidence: Provide the approved item described under Missing for WP-06, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -16120,8 +18958,11 @@
       <c r="G8" s="28" t="str">
         <v>Gregorian/7-digit/5-digit Julian dates disambiguated. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
+      <c r="H8" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="9" ht="144" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>WP-08</t>
@@ -16153,8 +18994,18 @@
       <c r="G9" s="28" t="str">
         <v>Rule-pattern and boundary regressions expanded. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. Remaining acceptance/input: CMS rare branch matrix and ordered tie baseline.</v>
       </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
+      <c r="H9" s="64" t="str">
+        <v>Item: WP-08 — Sample data is tiny
+Completed: Rule-pattern and boundary regressions expanded.
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: CMS rare branch matrix and ordered tie baseline.
+Requested evidence: Provide the approved item described under Missing for WP-08, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="10" ht="144" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>WP-09</t>
@@ -16186,8 +19037,18 @@
       <c r="G10" s="28" t="str">
         <v>Small synthetic functional suite passes. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. Remaining acceptance/input: Production-scale non-functional environment and acceptance limits.</v>
       </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
+      <c r="H10" s="64" t="str">
+        <v>Item: WP-09 — Volume and performance
+Completed: Small synthetic functional suite passes.
+Why still Blocked: The supplied small fixtures cannot demonstrate quarterly processing at 600–700 million records. Throughput and memory claims require a representative workload, production-like resources and an agreed service-level target.
+Missing: Production-scale non-functional environment and acceptance limits.
+Requested evidence: Provide a representative scale dataset or approved generator profile, target record/file volumes and distributions, production-like compute/storage configuration, and agreed elapsed-time/memory/restartability acceptance limits.
+Suggested responsible roles: Platform/performance team and business SLA owner.
+Closure criteria: Execute the scale run in that environment, retain volume/time/resource and recovery evidence, fix measured bottlenecks, and obtain acceptance against the agreed limits.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="11" ht="144" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>WP-10</t>
@@ -16219,8 +19080,18 @@
       <c r="G11" s="28" t="str">
         <v>Per-stage errors/bypass/statistics/decisions; Split record and signed charge balances. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. Remaining acceptance/input: CY/FY per-file control totals depend on routing spec.</v>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
+      <c r="H11" s="64" t="str">
+        <v>Item: WP-10 — Audit trail / balancing / counts
+Completed: Per-stage errors/bypass/statistics/decisions; Split record and signed charge balances.
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: CY/FY per-file control totals depend on routing spec.
+Requested evidence: Provide the approved item described under Missing for WP-10, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>WP-11</t>
@@ -16252,8 +19123,11 @@
       <c r="G12" s="28" t="str">
         <v>Rule6 enabled in supplied manifests. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. Remaining acceptance/input: None.</v>
       </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
+      <c r="H12" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="13" ht="144" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>WP-12</t>
@@ -16285,8 +19159,18 @@
       <c r="G13" s="28" t="str">
         <v>Documented differences reconciled where latest requirements are explicit. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. Remaining acceptance/input: Legacy &gt;45/index-collision differences need approved baseline.</v>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
+      <c r="H13" s="64" t="str">
+        <v>Item: WP-12 — Design differs from legacy by choice (LD-3137)
+Completed: Documented differences reconciled where latest requirements are explicit.
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Legacy &gt;45/index-collision differences need approved baseline.
+Requested evidence: Provide the approved item described under Missing for WP-12, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>WP-13</t>
@@ -16318,6 +19202,9 @@
       <c r="G14" s="28" t="str">
         <v>Case/spelling aliases retained and expanded. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. Remaining acceptance/input: None.</v>
       </c>
+      <c r="H14" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -16351,9 +19238,12 @@
       <c r="G15" s="28" t="str">
         <v>Outpatient/HHA not included in current IP/SNF project scope. Evidence: tests/unit/; tests/integration/test_demo_pipeline.py. </v>
       </c>
+      <c r="H15" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Excluded by the documented scope/deletion decision; no implementation is required unless scope changes.</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:H15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16364,7 +19254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -16372,6 +19262,7 @@
     <col width="110" customWidth="1" min="3" max="3"/>
     <col min="4" max="4" width="36" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="95" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="115" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -16396,6 +19287,9 @@
       <c r="E1" s="25" t="str">
         <v>Remarks by Srikanth</v>
       </c>
+      <c r="F1" s="61" t="str">
+        <v>Reason and closure requirements by Srikanth</v>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -16419,6 +19313,9 @@
       <c r="E2" s="28" t="str">
         <v>MM-FINAC21/22 takes precedence over inconsistent V3p20. Evidence: Document reconciliation; baseline-dependent.. Remaining acceptance/input: CMS baseline verification.</v>
       </c>
+      <c r="F2" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -16442,8 +19339,11 @@
       <c r="E3" s="28" t="str">
         <v>Final bypass covered&gt;LOS per October clarification. Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: None for specified direction.</v>
       </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
+      <c r="F3" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="4" ht="144" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CF-03</t>
@@ -16465,6 +19365,16 @@
       <c r="E4" s="28" t="str">
         <v>Deleted warning0640 blank/filler checked; internal warnings retained. Evidence: Document reconciliation; baseline-dependent.. Remaining acceptance/input: Owner confirmation of internal versus physical representation.</v>
       </c>
+      <c r="F4" s="64" t="str">
+        <v>Item: CF-03 — Warning 0640
+Completed: Deleted warning0640 blank/filler checked; internal warnings retained.
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Owner confirmation of internal versus physical representation.
+Requested evidence: Provide the approved item described under Missing for CF-03, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -16488,8 +19398,11 @@
       <c r="E5" s="28" t="str">
         <v>Admission exclusion applies to FA; Stay uses admission. Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: None for documented scope.</v>
       </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+      <c r="F5" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CF-05</t>
@@ -16511,8 +19424,11 @@
       <c r="E6" s="28" t="str">
         <v>MM-Stay15 last-bill diagnosis/procedure takes precedence over older accumulation research. Evidence: tests/unit/test_gap_register_business_rules.py; tests/unit/test_2026_discrepancy_updates.py. Remaining acceptance/input: CMS golden verification.</v>
       </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
+      <c r="F6" s="64" t="str">
+        <v>No pending implementation dependency recorded for this entry. Done refers to the documented QA check and cited regression evidence. It does not certify the complete production pipeline; production acceptance remains a separate project gate.</v>
+      </c>
+    </row>
+    <row r="7" ht="144" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>CF-06</t>
@@ -16534,8 +19450,18 @@
       <c r="E7" s="28" t="str">
         <v>Three bytes at FA plus three at Stay explain increments. Evidence: Document reconciliation; baseline-dependent.. Remaining acceptance/input: Exact flags/offsets from copybooks.</v>
       </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
+      <c r="F7" s="64" t="str">
+        <v>Item: CF-06 — Header bytes
+Completed: Three bytes at FA plus three at Stay explain increments.
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Exact flags/offsets from copybooks.
+Requested evidence: Provide the approved item described under Missing for CF-06, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="8" ht="144" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>CF-07</t>
@@ -16557,8 +19483,18 @@
       <c r="E8" s="28" t="str">
         <v>V3 states special-unit/outlier rules partly outdated. Evidence: Document reconciliation; baseline-dependent.. Remaining acceptance/input: Current MPRPARL/DRG/outlier baseline.</v>
       </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
+      <c r="F8" s="64" t="str">
+        <v>Item: CF-07 — Special unit code / outlier
+Completed: V3 states special-unit/outlier rules partly outdated.
+Why still Blocked: The remaining behavior is missing from, outdated in, or ambiguous between the supplied references. Only the owning business/legacy team can approve the authoritative decision table or current program mapping; choosing one interpretation silently could certify incorrect results.
+Missing: Current MPRPARL/DRG/outlier baseline.
+Requested evidence: Provide the approved item described under Missing for CF-07, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="9" ht="144" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>CF-08</t>
@@ -16580,8 +19516,18 @@
       <c r="E9" s="28" t="str">
         <v>Warning10 code2/3 duplicate text identified. Evidence: Document reconciliation; baseline-dependent.. Remaining acceptance/input: Approved distinct branch meanings.</v>
       </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
+      <c r="F9" s="64" t="str">
+        <v>Item: CF-08 — Warning 10 (RUGs)
+Completed: Warning10 code2/3 duplicate text identified.
+Why still Blocked: The remaining behavior is missing from, outdated in, or ambiguous between the supplied references. Only the owning business/legacy team can approve the authoritative decision table or current program mapping; choosing one interpretation silently could certify incorrect results.
+Missing: Approved distinct branch meanings.
+Requested evidence: Provide the approved item described under Missing for CF-08, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="10" ht="144" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>CF-09</t>
@@ -16603,8 +19549,18 @@
       <c r="E10" s="28" t="str">
         <v>LD-1421 recovered:7value amounts, FD and17 monetary direct fields distinguished. Evidence: Document reconciliation; baseline-dependent.. Remaining acceptance/input: Remaining source mappings and CMS fixture.</v>
       </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
+      <c r="F10" s="64" t="str">
+        <v>Item: CF-09 — Value-code fields
+Completed: LD-1421 recovered:7value amounts, FD and17 monetary direct fields distinguished.
+Why still Partial: The supplied documents do not establish this missing input or resolve the remaining rule completely. Guessing it would produce a check that may disagree with the approved production behavior.
+Missing: Remaining source mappings and CMS fixture.
+Requested evidence: Provide the approved item described under Missing for CF-09, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
+    </row>
+    <row r="11" ht="144" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>CF-10</t>
@@ -16626,9 +19582,19 @@
       <c r="E11" s="28" t="str">
         <v>All registered revenue totals now golden-compared. Evidence: Document reconciliation; baseline-dependent.. Remaining acceptance/input: Full40+revenue mapping; recovered LD-1514 still directs to MPRPARL.</v>
       </c>
+      <c r="F11" s="64" t="str">
+        <v>Item: CF-10 — Revenue totals 0890-1120
+Completed: All registered revenue totals now golden-compared.
+Why still Blocked: The remaining behavior is missing from, outdated in, or ambiguous between the supplied references. Only the owning business/legacy team can approve the authoritative decision table or current program mapping; choosing one interpretation silently could certify incorrect results.
+Missing: Full40+revenue mapping; recovered LD-1514 still directs to MPRPARL.
+Requested evidence: Provide the approved item described under Missing for CF-10, its effective version/date, and matched source/expected-output examples covering normal, boundary and exception cases.
+Suggested responsible roles: MedPAR business/legacy owner and the source-data team.
+Closure criteria: Implement or configure the approved remaining behavior, add regression cases for the supplied examples, then rerun the affected stage against the independently approved expected results with no unexplained differences. Record business acceptance separately from code completion.
+Can finish with current files: No — the cited approved input/decision or acceptance evidence is not present. Available local QA implementation and regression evidence are recorded in Remarks; no dependency is marked complete by assumption.</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:F11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>